--- a/zona_riska.xlsx
+++ b/zona_riska.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="10200" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="10200" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Инструкция" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9304" uniqueCount="1635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9304" uniqueCount="1636">
   <si>
     <t>Раздел</t>
   </si>
@@ -4942,6 +4942,9 @@
   </si>
   <si>
     <t>88</t>
+  </si>
+  <si>
+    <t>89</t>
   </si>
 </sst>
 </file>
@@ -27430,7 +27433,7 @@
         <v>66</v>
       </c>
       <c r="B456" s="4" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="C456" t="s">
         <v>68</v>

--- a/zona_riska.xlsx
+++ b/zona_riska.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9304" uniqueCount="1636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9304" uniqueCount="1635">
   <si>
     <t>Раздел</t>
   </si>
@@ -4941,10 +4941,7 @@
     <t>ТЧЭ-2 Нижнеудинск</t>
   </si>
   <si>
-    <t>88</t>
-  </si>
-  <si>
-    <t>89</t>
+    <t>90</t>
   </si>
 </sst>
 </file>
@@ -27433,7 +27430,7 @@
         <v>66</v>
       </c>
       <c r="B456" s="4" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="C456" t="s">
         <v>68</v>

--- a/zona_riska.xlsx
+++ b/zona_riska.xlsx
@@ -22,6 +22,7 @@
     <sheet name="Список узлов" sheetId="8" r:id="rId8"/>
     <sheet name="Пробег" sheetId="9" r:id="rId9"/>
     <sheet name="Места осмотра" sheetId="10" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Тест" sheetId="11" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">БИ!$A$1:$E$441</definedName>
@@ -4156,6 +4157,9528 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E470"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="4" max="4" width="36" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Серия</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Номер</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Приписка</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Место осмотра (необязательно)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Комментарий (необязательно)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">591</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">592</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">593</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">594</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">595</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">596</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">597</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">598</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">599</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">602</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">604</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">605</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">606</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">607</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">608</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">609</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">610</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">611</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">612</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">613</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">614</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">615</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">616</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">617</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">618</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">619</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">620</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">621</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">622</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">623</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">624</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">625</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">626</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">627</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">628</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">629</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">630</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">631</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">632</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">633</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">634</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">635</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">636</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">637</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">638</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">639</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">640</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">641</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">642</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">643</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">644</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">645</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">646</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">647</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">648</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">649</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">650</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">651</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">652</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">653</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">654</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">655</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">656</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">657</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">658</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">659</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">660</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">661</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">662</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">663</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">664</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">665</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">667</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">668</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">669</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">670</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">671</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">672</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">673</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-5 Кандалакша</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">674</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-5 Кандалакша</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">675</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-5 Кандалакша</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">676</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-5 Кандалакша</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">677</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-5 Кандалакша</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">678</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-5 Кандалакша</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">679</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-5 Кандалакша</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">680</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-5 Кандалакша</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">681</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-5 Кандалакша</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">682</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-5 Кандалакша</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">683</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-5 Кандалакша</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">684</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-5 Кандалакша</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">685</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-5 Кандалакша</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">686</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-5 Кандалакша</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">687</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-5 Кандалакша</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">688</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-5 Кандалакша</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">689</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">690</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">691</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">692</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">693</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">694</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">695</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">696</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">697</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">698</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">699</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">700</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">701</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">702</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">703</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">704</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">705</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">706</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">707</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">708</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">709</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">710</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">711</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">712</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">713</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">714</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">715</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">716</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">717</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">718</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">719</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">720</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B132" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">721</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">722</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">723</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">724</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">725</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B137" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">726</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B138" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">727</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">728</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">729</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B141" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">730</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B142" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">731</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B143" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">732</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B144" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">733</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B145" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">734</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B146" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">735</t>
+        </is>
+      </c>
+      <c r="C146" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B147" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">736</t>
+        </is>
+      </c>
+      <c r="C147" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B148" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">737</t>
+        </is>
+      </c>
+      <c r="C148" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B149" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">738</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B150" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">739</t>
+        </is>
+      </c>
+      <c r="C150" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B151" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">740</t>
+        </is>
+      </c>
+      <c r="C151" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B152" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">741</t>
+        </is>
+      </c>
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B153" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">742</t>
+        </is>
+      </c>
+      <c r="C153" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B154" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">743</t>
+        </is>
+      </c>
+      <c r="C154" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B155" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">744</t>
+        </is>
+      </c>
+      <c r="C155" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B156" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">745</t>
+        </is>
+      </c>
+      <c r="C156" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B157" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">746</t>
+        </is>
+      </c>
+      <c r="C157" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B158" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">747</t>
+        </is>
+      </c>
+      <c r="C158" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B159" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">748</t>
+        </is>
+      </c>
+      <c r="C159" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B160" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">749</t>
+        </is>
+      </c>
+      <c r="C160" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B161" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">750</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B162" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">751</t>
+        </is>
+      </c>
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B163" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">752</t>
+        </is>
+      </c>
+      <c r="C163" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B164" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">753</t>
+        </is>
+      </c>
+      <c r="C164" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B165" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">754</t>
+        </is>
+      </c>
+      <c r="C165" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B166" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">755</t>
+        </is>
+      </c>
+      <c r="C166" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B167" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">756</t>
+        </is>
+      </c>
+      <c r="C167" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B168" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">757</t>
+        </is>
+      </c>
+      <c r="C168" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B169" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">758</t>
+        </is>
+      </c>
+      <c r="C169" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B170" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">759</t>
+        </is>
+      </c>
+      <c r="C170" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B171" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">760</t>
+        </is>
+      </c>
+      <c r="C171" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B172" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">761</t>
+        </is>
+      </c>
+      <c r="C172" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B173" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">762</t>
+        </is>
+      </c>
+      <c r="C173" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B174" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">763</t>
+        </is>
+      </c>
+      <c r="C174" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B175" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">764</t>
+        </is>
+      </c>
+      <c r="C175" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B176" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">765</t>
+        </is>
+      </c>
+      <c r="C176" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B177" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">766</t>
+        </is>
+      </c>
+      <c r="C177" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B178" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">767</t>
+        </is>
+      </c>
+      <c r="C178" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B179" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">768</t>
+        </is>
+      </c>
+      <c r="C179" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B180" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">769</t>
+        </is>
+      </c>
+      <c r="C180" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B181" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">770</t>
+        </is>
+      </c>
+      <c r="C181" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B182" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">771</t>
+        </is>
+      </c>
+      <c r="C182" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-11 Тимашевская</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B183" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">772</t>
+        </is>
+      </c>
+      <c r="C183" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-5 Карталы</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B184" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">773</t>
+        </is>
+      </c>
+      <c r="C184" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-5 Карталы</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B185" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">774</t>
+        </is>
+      </c>
+      <c r="C185" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-5 Карталы</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B186" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">775</t>
+        </is>
+      </c>
+      <c r="C186" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-5 Карталы</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B187" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">776</t>
+        </is>
+      </c>
+      <c r="C187" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-5 Карталы</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B188" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">777</t>
+        </is>
+      </c>
+      <c r="C188" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-5 Карталы</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B189" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">778</t>
+        </is>
+      </c>
+      <c r="C189" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-5 Карталы</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B190" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">779</t>
+        </is>
+      </c>
+      <c r="C190" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-5 Карталы</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B191" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">780</t>
+        </is>
+      </c>
+      <c r="C191" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-5 Карталы</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B192" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">781</t>
+        </is>
+      </c>
+      <c r="C192" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-5 Карталы</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B193" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">782</t>
+        </is>
+      </c>
+      <c r="C193" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B194" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">783</t>
+        </is>
+      </c>
+      <c r="C194" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B195" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">784</t>
+        </is>
+      </c>
+      <c r="C195" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B196" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">785</t>
+        </is>
+      </c>
+      <c r="C196" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B197" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">786</t>
+        </is>
+      </c>
+      <c r="C197" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B198" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">787</t>
+        </is>
+      </c>
+      <c r="C198" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B199" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">788</t>
+        </is>
+      </c>
+      <c r="C199" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B200" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">789</t>
+        </is>
+      </c>
+      <c r="C200" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B201" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">790</t>
+        </is>
+      </c>
+      <c r="C201" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B202" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">791</t>
+        </is>
+      </c>
+      <c r="C202" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B203" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">792</t>
+        </is>
+      </c>
+      <c r="C203" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B204" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">793</t>
+        </is>
+      </c>
+      <c r="C204" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B205" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">794</t>
+        </is>
+      </c>
+      <c r="C205" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B206" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">795</t>
+        </is>
+      </c>
+      <c r="C206" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B207" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">796</t>
+        </is>
+      </c>
+      <c r="C207" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B208" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">797</t>
+        </is>
+      </c>
+      <c r="C208" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B209" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">798</t>
+        </is>
+      </c>
+      <c r="C209" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Петров Вал</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B210" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">799</t>
+        </is>
+      </c>
+      <c r="C210" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-14 Сальск</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B211" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="C211" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-14 Сальск</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B212" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">801</t>
+        </is>
+      </c>
+      <c r="C212" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-14 Сальск</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B213" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">802</t>
+        </is>
+      </c>
+      <c r="C213" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-14 Сальск</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B214" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">803</t>
+        </is>
+      </c>
+      <c r="C214" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-14 Сальск</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B215" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">804</t>
+        </is>
+      </c>
+      <c r="C215" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-14 Сальск</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B216" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">805</t>
+        </is>
+      </c>
+      <c r="C216" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-14 Сальск</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B217" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">806</t>
+        </is>
+      </c>
+      <c r="C217" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-14 Сальск</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B218" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">807</t>
+        </is>
+      </c>
+      <c r="C218" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-14 Сальск</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B219" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">808</t>
+        </is>
+      </c>
+      <c r="C219" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-14 Сальск</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B220" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">809</t>
+        </is>
+      </c>
+      <c r="C220" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-14 Сальск</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B221" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810</t>
+        </is>
+      </c>
+      <c r="C221" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-14 Сальск</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B222" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">811</t>
+        </is>
+      </c>
+      <c r="C222" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-14 Сальск</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B223" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">812</t>
+        </is>
+      </c>
+      <c r="C223" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-14 Сальск</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B224" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">813</t>
+        </is>
+      </c>
+      <c r="C224" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-14 Сальск</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B225" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">814</t>
+        </is>
+      </c>
+      <c r="C225" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-14 Сальск</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B226" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">815</t>
+        </is>
+      </c>
+      <c r="C226" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-14 Сальск</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B227" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">816</t>
+        </is>
+      </c>
+      <c r="C227" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-14 Сальск</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B228" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">817</t>
+        </is>
+      </c>
+      <c r="C228" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-14 Сальск</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B229" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">818</t>
+        </is>
+      </c>
+      <c r="C229" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-14 Сальск</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B230" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">819</t>
+        </is>
+      </c>
+      <c r="C230" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-9 Лянгасово</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B231" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">820</t>
+        </is>
+      </c>
+      <c r="C231" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-9 Лянгасово</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B232" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">821</t>
+        </is>
+      </c>
+      <c r="C232" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-9 Лянгасово</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B233" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">822</t>
+        </is>
+      </c>
+      <c r="C233" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-9 Лянгасово</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B234" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">823</t>
+        </is>
+      </c>
+      <c r="C234" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-9 Лянгасово</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B235" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">824</t>
+        </is>
+      </c>
+      <c r="C235" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-9 Лянгасово</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B236" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">825</t>
+        </is>
+      </c>
+      <c r="C236" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-9 Лянгасово</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B237" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">826</t>
+        </is>
+      </c>
+      <c r="C237" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-9 Лянгасово</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B238" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">827</t>
+        </is>
+      </c>
+      <c r="C238" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-9 Лянгасово</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B239" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">828</t>
+        </is>
+      </c>
+      <c r="C239" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-9 Лянгасово</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B240" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">829</t>
+        </is>
+      </c>
+      <c r="C240" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-9 Лянгасово</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2ЭС5К</t>
+        </is>
+      </c>
+      <c r="B241" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">830</t>
+        </is>
+      </c>
+      <c r="C241" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-9 Лянгасово</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B242" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1515</t>
+        </is>
+      </c>
+      <c r="C242" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-3 Чита</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B243" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1516</t>
+        </is>
+      </c>
+      <c r="C243" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-3 Чита</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B244" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1517</t>
+        </is>
+      </c>
+      <c r="C244" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-3 Чита</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B245" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1518</t>
+        </is>
+      </c>
+      <c r="C245" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-3 Чита</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B246" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1519</t>
+        </is>
+      </c>
+      <c r="C246" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-3 Чита</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B247" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1520</t>
+        </is>
+      </c>
+      <c r="C247" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-3 Чита</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B248" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1521</t>
+        </is>
+      </c>
+      <c r="C248" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-3 Чита</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B249" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1522</t>
+        </is>
+      </c>
+      <c r="C249" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-3 Чита</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B250" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1523</t>
+        </is>
+      </c>
+      <c r="C250" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-3 Чита</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B251" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1524</t>
+        </is>
+      </c>
+      <c r="C251" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-3 Чита</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B252" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1525</t>
+        </is>
+      </c>
+      <c r="C252" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B253" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1526</t>
+        </is>
+      </c>
+      <c r="C253" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B254" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1527</t>
+        </is>
+      </c>
+      <c r="C254" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B255" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1528</t>
+        </is>
+      </c>
+      <c r="C255" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B256" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1529</t>
+        </is>
+      </c>
+      <c r="C256" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B257" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1530</t>
+        </is>
+      </c>
+      <c r="C257" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B258" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1531</t>
+        </is>
+      </c>
+      <c r="C258" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B259" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1532</t>
+        </is>
+      </c>
+      <c r="C259" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B260" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1533</t>
+        </is>
+      </c>
+      <c r="C260" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B261" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1534</t>
+        </is>
+      </c>
+      <c r="C261" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B262" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1535</t>
+        </is>
+      </c>
+      <c r="C262" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B263" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1536</t>
+        </is>
+      </c>
+      <c r="C263" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B264" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1537</t>
+        </is>
+      </c>
+      <c r="C264" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B265" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1538</t>
+        </is>
+      </c>
+      <c r="C265" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B266" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1539</t>
+        </is>
+      </c>
+      <c r="C266" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B267" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1540</t>
+        </is>
+      </c>
+      <c r="C267" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B268" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1541</t>
+        </is>
+      </c>
+      <c r="C268" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B269" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1542</t>
+        </is>
+      </c>
+      <c r="C269" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B270" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1543</t>
+        </is>
+      </c>
+      <c r="C270" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B271" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1544</t>
+        </is>
+      </c>
+      <c r="C271" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B272" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1545</t>
+        </is>
+      </c>
+      <c r="C272" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B273" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1546</t>
+        </is>
+      </c>
+      <c r="C273" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B274" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1547</t>
+        </is>
+      </c>
+      <c r="C274" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B275" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1548</t>
+        </is>
+      </c>
+      <c r="C275" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B276" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1549</t>
+        </is>
+      </c>
+      <c r="C276" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B277" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1550</t>
+        </is>
+      </c>
+      <c r="C277" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B278" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1551</t>
+        </is>
+      </c>
+      <c r="C278" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B279" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1552</t>
+        </is>
+      </c>
+      <c r="C279" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B280" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1553</t>
+        </is>
+      </c>
+      <c r="C280" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B281" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1554</t>
+        </is>
+      </c>
+      <c r="C281" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B282" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1555</t>
+        </is>
+      </c>
+      <c r="C282" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B283" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1556</t>
+        </is>
+      </c>
+      <c r="C283" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B284" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1557</t>
+        </is>
+      </c>
+      <c r="C284" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B285" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1558</t>
+        </is>
+      </c>
+      <c r="C285" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B286" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1559</t>
+        </is>
+      </c>
+      <c r="C286" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B287" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1560</t>
+        </is>
+      </c>
+      <c r="C287" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B288" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1561</t>
+        </is>
+      </c>
+      <c r="C288" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B289" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1562</t>
+        </is>
+      </c>
+      <c r="C289" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B290" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1563</t>
+        </is>
+      </c>
+      <c r="C290" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B291" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1564</t>
+        </is>
+      </c>
+      <c r="C291" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B292" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1565</t>
+        </is>
+      </c>
+      <c r="C292" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B293" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1566</t>
+        </is>
+      </c>
+      <c r="C293" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B294" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1567</t>
+        </is>
+      </c>
+      <c r="C294" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B295" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1568</t>
+        </is>
+      </c>
+      <c r="C295" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B296" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1569</t>
+        </is>
+      </c>
+      <c r="C296" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B297" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1570</t>
+        </is>
+      </c>
+      <c r="C297" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B298" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1571</t>
+        </is>
+      </c>
+      <c r="C298" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B299" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1572</t>
+        </is>
+      </c>
+      <c r="C299" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B300" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1573</t>
+        </is>
+      </c>
+      <c r="C300" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B301" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1574</t>
+        </is>
+      </c>
+      <c r="C301" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B302" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1575</t>
+        </is>
+      </c>
+      <c r="C302" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-10 Карасук</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B303" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1576</t>
+        </is>
+      </c>
+      <c r="C303" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B304" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1577</t>
+        </is>
+      </c>
+      <c r="C304" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B305" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1578</t>
+        </is>
+      </c>
+      <c r="C305" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B306" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1579</t>
+        </is>
+      </c>
+      <c r="C306" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B307" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1580</t>
+        </is>
+      </c>
+      <c r="C307" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B308" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1581</t>
+        </is>
+      </c>
+      <c r="C308" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B309" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1582</t>
+        </is>
+      </c>
+      <c r="C309" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B310" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1583</t>
+        </is>
+      </c>
+      <c r="C310" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B311" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1584</t>
+        </is>
+      </c>
+      <c r="C311" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B312" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1585</t>
+        </is>
+      </c>
+      <c r="C312" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B313" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1586</t>
+        </is>
+      </c>
+      <c r="C313" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B314" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1587</t>
+        </is>
+      </c>
+      <c r="C314" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B315" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1588</t>
+        </is>
+      </c>
+      <c r="C315" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B316" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1589</t>
+        </is>
+      </c>
+      <c r="C316" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B317" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1590</t>
+        </is>
+      </c>
+      <c r="C317" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B318" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1591</t>
+        </is>
+      </c>
+      <c r="C318" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B319" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1592</t>
+        </is>
+      </c>
+      <c r="C319" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B320" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1593</t>
+        </is>
+      </c>
+      <c r="C320" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B321" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1594</t>
+        </is>
+      </c>
+      <c r="C321" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B322" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1595</t>
+        </is>
+      </c>
+      <c r="C322" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B323" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1596</t>
+        </is>
+      </c>
+      <c r="C323" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B324" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1597</t>
+        </is>
+      </c>
+      <c r="C324" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B325" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1598</t>
+        </is>
+      </c>
+      <c r="C325" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B326" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1599</t>
+        </is>
+      </c>
+      <c r="C326" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B327" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1600</t>
+        </is>
+      </c>
+      <c r="C327" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B328" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1601</t>
+        </is>
+      </c>
+      <c r="C328" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B329" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1602</t>
+        </is>
+      </c>
+      <c r="C329" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B330" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1603</t>
+        </is>
+      </c>
+      <c r="C330" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B331" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1604</t>
+        </is>
+      </c>
+      <c r="C331" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B332" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1605</t>
+        </is>
+      </c>
+      <c r="C332" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B333" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1606</t>
+        </is>
+      </c>
+      <c r="C333" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B334" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1607</t>
+        </is>
+      </c>
+      <c r="C334" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B335" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1608</t>
+        </is>
+      </c>
+      <c r="C335" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B336" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1609</t>
+        </is>
+      </c>
+      <c r="C336" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B337" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1610</t>
+        </is>
+      </c>
+      <c r="C337" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B338" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1611</t>
+        </is>
+      </c>
+      <c r="C338" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B339" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1612</t>
+        </is>
+      </c>
+      <c r="C339" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B340" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1613</t>
+        </is>
+      </c>
+      <c r="C340" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B341" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1614</t>
+        </is>
+      </c>
+      <c r="C341" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B342" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1615</t>
+        </is>
+      </c>
+      <c r="C342" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B343" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1616</t>
+        </is>
+      </c>
+      <c r="C343" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B344" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1617</t>
+        </is>
+      </c>
+      <c r="C344" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B345" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1618</t>
+        </is>
+      </c>
+      <c r="C345" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B346" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1619</t>
+        </is>
+      </c>
+      <c r="C346" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B347" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1620</t>
+        </is>
+      </c>
+      <c r="C347" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B348" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1621</t>
+        </is>
+      </c>
+      <c r="C348" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B349" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1622</t>
+        </is>
+      </c>
+      <c r="C349" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B350" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1623</t>
+        </is>
+      </c>
+      <c r="C350" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B351" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1624</t>
+        </is>
+      </c>
+      <c r="C351" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B352" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1625</t>
+        </is>
+      </c>
+      <c r="C352" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B353" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1626</t>
+        </is>
+      </c>
+      <c r="C353" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B354" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1627</t>
+        </is>
+      </c>
+      <c r="C354" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B355" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1628</t>
+        </is>
+      </c>
+      <c r="C355" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B356" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1629</t>
+        </is>
+      </c>
+      <c r="C356" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B357" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1630</t>
+        </is>
+      </c>
+      <c r="C357" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B358" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1631</t>
+        </is>
+      </c>
+      <c r="C358" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B359" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1632</t>
+        </is>
+      </c>
+      <c r="C359" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B360" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1633</t>
+        </is>
+      </c>
+      <c r="C360" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B361" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1634</t>
+        </is>
+      </c>
+      <c r="C361" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B362" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1635</t>
+        </is>
+      </c>
+      <c r="C362" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B363" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1636</t>
+        </is>
+      </c>
+      <c r="C363" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B364" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1637</t>
+        </is>
+      </c>
+      <c r="C364" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B365" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1638</t>
+        </is>
+      </c>
+      <c r="C365" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B366" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1639</t>
+        </is>
+      </c>
+      <c r="C366" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B367" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1640</t>
+        </is>
+      </c>
+      <c r="C367" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B368" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1641</t>
+        </is>
+      </c>
+      <c r="C368" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B369" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1642</t>
+        </is>
+      </c>
+      <c r="C369" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B370" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1643</t>
+        </is>
+      </c>
+      <c r="C370" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B371" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1644</t>
+        </is>
+      </c>
+      <c r="C371" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B372" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1645</t>
+        </is>
+      </c>
+      <c r="C372" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B373" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1646</t>
+        </is>
+      </c>
+      <c r="C373" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B374" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1647</t>
+        </is>
+      </c>
+      <c r="C374" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B375" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1648</t>
+        </is>
+      </c>
+      <c r="C375" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B376" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1649</t>
+        </is>
+      </c>
+      <c r="C376" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B377" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1650</t>
+        </is>
+      </c>
+      <c r="C377" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B378" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1651</t>
+        </is>
+      </c>
+      <c r="C378" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B379" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1652</t>
+        </is>
+      </c>
+      <c r="C379" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B380" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1653</t>
+        </is>
+      </c>
+      <c r="C380" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B381" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1654</t>
+        </is>
+      </c>
+      <c r="C381" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B382" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1655</t>
+        </is>
+      </c>
+      <c r="C382" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B383" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1656</t>
+        </is>
+      </c>
+      <c r="C383" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B384" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1657</t>
+        </is>
+      </c>
+      <c r="C384" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B385" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1658</t>
+        </is>
+      </c>
+      <c r="C385" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B386" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1659</t>
+        </is>
+      </c>
+      <c r="C386" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B387" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1660</t>
+        </is>
+      </c>
+      <c r="C387" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B388" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1661</t>
+        </is>
+      </c>
+      <c r="C388" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B389" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1662</t>
+        </is>
+      </c>
+      <c r="C389" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B390" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1663</t>
+        </is>
+      </c>
+      <c r="C390" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B391" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1664</t>
+        </is>
+      </c>
+      <c r="C391" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B392" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1665</t>
+        </is>
+      </c>
+      <c r="C392" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B393" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1666</t>
+        </is>
+      </c>
+      <c r="C393" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B394" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1667</t>
+        </is>
+      </c>
+      <c r="C394" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B395" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1668</t>
+        </is>
+      </c>
+      <c r="C395" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B396" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1669</t>
+        </is>
+      </c>
+      <c r="C396" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B397" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1670</t>
+        </is>
+      </c>
+      <c r="C397" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B398" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1671</t>
+        </is>
+      </c>
+      <c r="C398" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B399" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1672</t>
+        </is>
+      </c>
+      <c r="C399" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B400" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1673</t>
+        </is>
+      </c>
+      <c r="C400" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B401" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1674</t>
+        </is>
+      </c>
+      <c r="C401" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B402" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1675</t>
+        </is>
+      </c>
+      <c r="C402" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B403" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1676</t>
+        </is>
+      </c>
+      <c r="C403" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B404" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1677</t>
+        </is>
+      </c>
+      <c r="C404" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B405" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1678</t>
+        </is>
+      </c>
+      <c r="C405" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B406" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1679</t>
+        </is>
+      </c>
+      <c r="C406" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B407" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1680</t>
+        </is>
+      </c>
+      <c r="C407" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B408" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1681</t>
+        </is>
+      </c>
+      <c r="C408" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B409" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1682</t>
+        </is>
+      </c>
+      <c r="C409" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B410" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1683</t>
+        </is>
+      </c>
+      <c r="C410" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B411" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1684</t>
+        </is>
+      </c>
+      <c r="C411" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B412" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1685</t>
+        </is>
+      </c>
+      <c r="C412" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B413" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1686</t>
+        </is>
+      </c>
+      <c r="C413" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B414" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1687</t>
+        </is>
+      </c>
+      <c r="C414" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B415" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1688</t>
+        </is>
+      </c>
+      <c r="C415" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B416" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1689</t>
+        </is>
+      </c>
+      <c r="C416" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B417" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1690</t>
+        </is>
+      </c>
+      <c r="C417" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B418" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1691</t>
+        </is>
+      </c>
+      <c r="C418" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B419" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1692</t>
+        </is>
+      </c>
+      <c r="C419" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B420" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1693</t>
+        </is>
+      </c>
+      <c r="C420" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B421" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1694</t>
+        </is>
+      </c>
+      <c r="C421" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B422" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1695</t>
+        </is>
+      </c>
+      <c r="C422" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B423" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1696</t>
+        </is>
+      </c>
+      <c r="C423" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B424" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1697</t>
+        </is>
+      </c>
+      <c r="C424" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B425" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1698</t>
+        </is>
+      </c>
+      <c r="C425" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B426" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1699</t>
+        </is>
+      </c>
+      <c r="C426" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B427" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1700</t>
+        </is>
+      </c>
+      <c r="C427" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B428" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1701</t>
+        </is>
+      </c>
+      <c r="C428" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B429" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1702</t>
+        </is>
+      </c>
+      <c r="C429" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B430" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1703</t>
+        </is>
+      </c>
+      <c r="C430" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B431" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1704</t>
+        </is>
+      </c>
+      <c r="C431" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B432" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1705</t>
+        </is>
+      </c>
+      <c r="C432" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B433" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1706</t>
+        </is>
+      </c>
+      <c r="C433" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ЭС5К</t>
+        </is>
+      </c>
+      <c r="B434" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66</t>
+        </is>
+      </c>
+      <c r="C434" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-8 Смоляниново</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ЭС5К</t>
+        </is>
+      </c>
+      <c r="B435" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">67</t>
+        </is>
+      </c>
+      <c r="C435" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-8 Смоляниново</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ЭС5К</t>
+        </is>
+      </c>
+      <c r="B436" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68</t>
+        </is>
+      </c>
+      <c r="C436" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-8 Смоляниново</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ЭС5К</t>
+        </is>
+      </c>
+      <c r="B437" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69</t>
+        </is>
+      </c>
+      <c r="C437" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-8 Смоляниново</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ЭС5К</t>
+        </is>
+      </c>
+      <c r="B438" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70</t>
+        </is>
+      </c>
+      <c r="C438" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-8 Смоляниново</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ЭС5К</t>
+        </is>
+      </c>
+      <c r="B439" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">71</t>
+        </is>
+      </c>
+      <c r="C439" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-8 Смоляниново</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ЭС5К</t>
+        </is>
+      </c>
+      <c r="B440" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72</t>
+        </is>
+      </c>
+      <c r="C440" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-8 Смоляниново</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ЭС5К</t>
+        </is>
+      </c>
+      <c r="B441" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">73</t>
+        </is>
+      </c>
+      <c r="C441" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-8 Смоляниново</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ЭС5К</t>
+        </is>
+      </c>
+      <c r="B442" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74</t>
+        </is>
+      </c>
+      <c r="C442" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-8 Смоляниново</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ЭС5К</t>
+        </is>
+      </c>
+      <c r="B443" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">75</t>
+        </is>
+      </c>
+      <c r="C443" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-8 Смоляниново</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ЭС5К</t>
+        </is>
+      </c>
+      <c r="B444" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">76</t>
+        </is>
+      </c>
+      <c r="C444" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-8 Смоляниново</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ЭС5К</t>
+        </is>
+      </c>
+      <c r="B445" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77</t>
+        </is>
+      </c>
+      <c r="C445" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-8 Смоляниново</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ЭС5К</t>
+        </is>
+      </c>
+      <c r="B446" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78</t>
+        </is>
+      </c>
+      <c r="C446" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-8 Смоляниново</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ЭС5К</t>
+        </is>
+      </c>
+      <c r="B447" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79</t>
+        </is>
+      </c>
+      <c r="C447" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-8 Смоляниново</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ЭС5К</t>
+        </is>
+      </c>
+      <c r="B448" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80</t>
+        </is>
+      </c>
+      <c r="C448" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-8 Смоляниново</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ЭС5К</t>
+        </is>
+      </c>
+      <c r="B449" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81</t>
+        </is>
+      </c>
+      <c r="C449" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-8 Смоляниново</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ЭС5К</t>
+        </is>
+      </c>
+      <c r="B450" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82</t>
+        </is>
+      </c>
+      <c r="C450" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-8 Смоляниново</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ЭС5К</t>
+        </is>
+      </c>
+      <c r="B451" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">83</t>
+        </is>
+      </c>
+      <c r="C451" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-8 Смоляниново</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ЭС5К</t>
+        </is>
+      </c>
+      <c r="B452" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84</t>
+        </is>
+      </c>
+      <c r="C452" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-8 Смоляниново</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ЭС5К</t>
+        </is>
+      </c>
+      <c r="B453" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">85</t>
+        </is>
+      </c>
+      <c r="C453" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-8 Смоляниново</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ЭС5К</t>
+        </is>
+      </c>
+      <c r="B454" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86</t>
+        </is>
+      </c>
+      <c r="C454" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-8 Смоляниново</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ЭС5К</t>
+        </is>
+      </c>
+      <c r="B455" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87</t>
+        </is>
+      </c>
+      <c r="C455" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-8 Смоляниново</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B456" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1707</t>
+        </is>
+      </c>
+      <c r="C456" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B457" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1708</t>
+        </is>
+      </c>
+      <c r="C457" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B458" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1709</t>
+        </is>
+      </c>
+      <c r="C458" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B459" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1710</t>
+        </is>
+      </c>
+      <c r="C459" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B460" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1711</t>
+        </is>
+      </c>
+      <c r="C460" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B461" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1712</t>
+        </is>
+      </c>
+      <c r="C461" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B462" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1713</t>
+        </is>
+      </c>
+      <c r="C462" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B463" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1714</t>
+        </is>
+      </c>
+      <c r="C463" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B464" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1715</t>
+        </is>
+      </c>
+      <c r="C464" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B465" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1716</t>
+        </is>
+      </c>
+      <c r="C465" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B466" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1717</t>
+        </is>
+      </c>
+      <c r="C466" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B467" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1718</t>
+        </is>
+      </c>
+      <c r="C467" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B468" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1719</t>
+        </is>
+      </c>
+      <c r="C468" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ЭС5К</t>
+        </is>
+      </c>
+      <c r="B469" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88</t>
+        </is>
+      </c>
+      <c r="C469" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-8 Смоляниново</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4ЭС5К</t>
+        </is>
+      </c>
+      <c r="B470" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89</t>
+        </is>
+      </c>
+      <c r="C470" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-8 Смоляниново</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="5"/>
+      <c r="B471" s="6"/>
+      <c r="C471" s="5"/>
+    </row>
+    <row r="472">
+      <c r="A472" s="5"/>
+      <c r="B472" s="6"/>
+      <c r="C472" s="5"/>
+    </row>
+    <row r="473">
+      <c r="A473" s="5"/>
+      <c r="B473" s="6"/>
+      <c r="C473" s="5"/>
+    </row>
+    <row r="474">
+      <c r="A474" s="5"/>
+      <c r="B474" s="6"/>
+      <c r="C474" s="5"/>
+    </row>
+    <row r="475">
+      <c r="A475" s="5"/>
+      <c r="B475" s="6"/>
+      <c r="C475" s="5"/>
+    </row>
+    <row r="476">
+      <c r="A476" s="5"/>
+      <c r="B476" s="6"/>
+      <c r="C476" s="5"/>
+    </row>
+    <row r="477">
+      <c r="A477" s="5"/>
+      <c r="B477" s="6"/>
+      <c r="C477" s="5"/>
+    </row>
+    <row r="478">
+      <c r="A478" s="5"/>
+      <c r="B478" s="6"/>
+      <c r="C478" s="5"/>
+    </row>
+    <row r="479">
+      <c r="A479" s="5"/>
+      <c r="B479" s="6"/>
+      <c r="C479" s="5"/>
+    </row>
+    <row r="480">
+      <c r="A480" s="5"/>
+      <c r="B480" s="6"/>
+      <c r="C480" s="5"/>
+    </row>
+    <row r="481">
+      <c r="A481" s="5"/>
+      <c r="B481" s="6"/>
+      <c r="C481" s="5"/>
+    </row>
+    <row r="482">
+      <c r="A482" s="5"/>
+      <c r="B482" s="6"/>
+      <c r="C482" s="5"/>
+    </row>
+    <row r="483">
+      <c r="A483" s="5"/>
+      <c r="B483" s="6"/>
+      <c r="C483" s="5"/>
+    </row>
+    <row r="484">
+      <c r="A484" s="5"/>
+      <c r="B484" s="6"/>
+      <c r="C484" s="5"/>
+    </row>
+    <row r="485">
+      <c r="A485" s="5"/>
+      <c r="B485" s="6"/>
+      <c r="C485" s="5"/>
+    </row>
+    <row r="486">
+      <c r="A486" s="5"/>
+      <c r="B486" s="6"/>
+      <c r="C486" s="5"/>
+    </row>
+    <row r="487">
+      <c r="A487" s="5"/>
+      <c r="B487" s="6"/>
+      <c r="C487" s="5"/>
+    </row>
+    <row r="488">
+      <c r="A488" s="5"/>
+      <c r="B488" s="6"/>
+      <c r="C488" s="5"/>
+    </row>
+    <row r="489">
+      <c r="A489" s="5"/>
+      <c r="B489" s="6"/>
+      <c r="C489" s="5"/>
+    </row>
+    <row r="490">
+      <c r="A490" s="5"/>
+      <c r="B490" s="6"/>
+      <c r="C490" s="5"/>
+    </row>
+    <row r="491">
+      <c r="A491" s="5"/>
+      <c r="B491" s="6"/>
+      <c r="C491" s="5"/>
+    </row>
+    <row r="492">
+      <c r="A492" s="5"/>
+      <c r="B492" s="6"/>
+      <c r="C492" s="5"/>
+    </row>
+    <row r="493">
+      <c r="A493" s="5"/>
+      <c r="B493" s="6"/>
+      <c r="C493" s="5"/>
+    </row>
+    <row r="494">
+      <c r="A494" s="5"/>
+      <c r="B494" s="6"/>
+      <c r="C494" s="5"/>
+    </row>
+    <row r="495">
+      <c r="A495" s="5"/>
+      <c r="B495" s="6"/>
+      <c r="C495" s="5"/>
+    </row>
+    <row r="496">
+      <c r="A496" s="5"/>
+      <c r="B496" s="6"/>
+      <c r="C496" s="5"/>
+    </row>
+    <row r="497">
+      <c r="A497" s="5"/>
+      <c r="B497" s="6"/>
+      <c r="C497" s="5"/>
+    </row>
+    <row r="498">
+      <c r="A498" s="5"/>
+      <c r="B498" s="6"/>
+      <c r="C498" s="5"/>
+    </row>
+    <row r="499">
+      <c r="A499" s="5"/>
+      <c r="B499" s="6"/>
+      <c r="C499" s="5"/>
+    </row>
+    <row r="500">
+      <c r="A500" s="5"/>
+      <c r="B500" s="6"/>
+      <c r="C500" s="5"/>
+    </row>
+    <row r="501">
+      <c r="A501" s="5"/>
+      <c r="B501" s="6"/>
+      <c r="C501" s="5"/>
+    </row>
+    <row r="502">
+      <c r="A502" s="5"/>
+      <c r="B502" s="6"/>
+      <c r="C502" s="5"/>
+    </row>
+    <row r="503">
+      <c r="A503" s="5"/>
+      <c r="B503" s="6"/>
+      <c r="C503" s="5"/>
+    </row>
+    <row r="504">
+      <c r="A504" s="5"/>
+      <c r="B504" s="6"/>
+      <c r="C504" s="5"/>
+    </row>
+    <row r="505">
+      <c r="A505" s="5"/>
+      <c r="B505" s="6"/>
+      <c r="C505" s="5"/>
+    </row>
+    <row r="506">
+      <c r="A506" s="5"/>
+      <c r="B506" s="6"/>
+      <c r="C506" s="5"/>
+    </row>
+    <row r="507">
+      <c r="A507" s="5"/>
+      <c r="B507" s="6"/>
+      <c r="C507" s="5"/>
+    </row>
+    <row r="508">
+      <c r="A508" s="5"/>
+      <c r="B508" s="6"/>
+      <c r="C508" s="5"/>
+    </row>
+    <row r="509">
+      <c r="A509" s="5"/>
+      <c r="B509" s="6"/>
+      <c r="C509" s="5"/>
+    </row>
+    <row r="510">
+      <c r="A510" s="5"/>
+      <c r="B510" s="6"/>
+      <c r="C510" s="5"/>
+    </row>
+    <row r="511">
+      <c r="A511" s="5"/>
+      <c r="B511" s="6"/>
+      <c r="C511" s="5"/>
+    </row>
+    <row r="512">
+      <c r="A512" s="5"/>
+      <c r="B512" s="6"/>
+      <c r="C512" s="5"/>
+    </row>
+    <row r="513">
+      <c r="A513" s="5"/>
+      <c r="B513" s="6"/>
+      <c r="C513" s="5"/>
+    </row>
+    <row r="514">
+      <c r="A514" s="5"/>
+      <c r="B514" s="6"/>
+      <c r="C514" s="5"/>
+    </row>
+    <row r="515">
+      <c r="A515" s="5"/>
+      <c r="B515" s="6"/>
+      <c r="C515" s="5"/>
+    </row>
+    <row r="516">
+      <c r="A516" s="5"/>
+      <c r="B516" s="6"/>
+      <c r="C516" s="5"/>
+    </row>
+    <row r="517">
+      <c r="A517" s="5"/>
+      <c r="B517" s="6"/>
+      <c r="C517" s="5"/>
+    </row>
+    <row r="518">
+      <c r="A518" s="5"/>
+      <c r="B518" s="6"/>
+      <c r="C518" s="5"/>
+    </row>
+    <row r="519">
+      <c r="A519" s="5"/>
+      <c r="B519" s="6"/>
+      <c r="C519" s="5"/>
+    </row>
+    <row r="520">
+      <c r="A520" s="5"/>
+      <c r="B520" s="6"/>
+      <c r="C520" s="5"/>
+    </row>
+    <row r="521">
+      <c r="A521" s="5"/>
+      <c r="B521" s="6"/>
+      <c r="C521" s="5"/>
+    </row>
+    <row r="522">
+      <c r="A522" s="5"/>
+      <c r="B522" s="6"/>
+      <c r="C522" s="5"/>
+    </row>
+    <row r="523">
+      <c r="A523" s="5"/>
+      <c r="B523" s="6"/>
+      <c r="C523" s="5"/>
+    </row>
+    <row r="524">
+      <c r="A524" s="5"/>
+      <c r="B524" s="6"/>
+      <c r="C524" s="5"/>
+    </row>
+    <row r="525">
+      <c r="A525" s="5"/>
+      <c r="B525" s="6"/>
+      <c r="C525" s="5"/>
+    </row>
+    <row r="526">
+      <c r="A526" s="5"/>
+      <c r="B526" s="6"/>
+      <c r="C526" s="5"/>
+    </row>
+    <row r="527">
+      <c r="A527" s="5"/>
+      <c r="B527" s="6"/>
+      <c r="C527" s="5"/>
+    </row>
+    <row r="528">
+      <c r="A528" s="5"/>
+      <c r="B528" s="6"/>
+      <c r="C528" s="5"/>
+    </row>
+    <row r="529">
+      <c r="A529" s="5"/>
+      <c r="B529" s="6"/>
+      <c r="C529" s="5"/>
+    </row>
+    <row r="530">
+      <c r="A530" s="5"/>
+      <c r="B530" s="6"/>
+      <c r="C530" s="5"/>
+    </row>
+    <row r="531">
+      <c r="A531" s="5"/>
+      <c r="B531" s="6"/>
+      <c r="C531" s="5"/>
+    </row>
+    <row r="532">
+      <c r="A532" s="5"/>
+      <c r="B532" s="6"/>
+      <c r="C532" s="5"/>
+    </row>
+    <row r="533">
+      <c r="A533" s="5"/>
+      <c r="B533" s="6"/>
+      <c r="C533" s="5"/>
+    </row>
+    <row r="534">
+      <c r="A534" s="5"/>
+      <c r="B534" s="6"/>
+      <c r="C534" s="5"/>
+    </row>
+    <row r="535">
+      <c r="A535" s="5"/>
+      <c r="B535" s="6"/>
+      <c r="C535" s="5"/>
+    </row>
+    <row r="536">
+      <c r="A536" s="5"/>
+      <c r="B536" s="6"/>
+      <c r="C536" s="5"/>
+    </row>
+    <row r="537">
+      <c r="A537" s="5"/>
+      <c r="B537" s="6"/>
+      <c r="C537" s="5"/>
+    </row>
+    <row r="538">
+      <c r="A538" s="5"/>
+      <c r="B538" s="6"/>
+      <c r="C538" s="5"/>
+    </row>
+    <row r="539">
+      <c r="A539" s="5"/>
+      <c r="B539" s="6"/>
+      <c r="C539" s="5"/>
+    </row>
+    <row r="540">
+      <c r="A540" s="5"/>
+      <c r="B540" s="6"/>
+      <c r="C540" s="5"/>
+    </row>
+    <row r="541">
+      <c r="A541" s="5"/>
+      <c r="B541" s="6"/>
+      <c r="C541" s="5"/>
+    </row>
+    <row r="542">
+      <c r="A542" s="5"/>
+      <c r="B542" s="6"/>
+      <c r="C542" s="5"/>
+    </row>
+    <row r="543">
+      <c r="A543" s="5"/>
+      <c r="B543" s="6"/>
+      <c r="C543" s="5"/>
+    </row>
+    <row r="544">
+      <c r="A544" s="5"/>
+      <c r="B544" s="6"/>
+      <c r="C544" s="5"/>
+    </row>
+    <row r="545">
+      <c r="A545" s="5"/>
+      <c r="B545" s="6"/>
+      <c r="C545" s="5"/>
+    </row>
+    <row r="546">
+      <c r="A546" s="5"/>
+      <c r="B546" s="6"/>
+      <c r="C546" s="5"/>
+    </row>
+    <row r="547">
+      <c r="A547" s="5"/>
+      <c r="B547" s="6"/>
+      <c r="C547" s="5"/>
+    </row>
+    <row r="548">
+      <c r="A548" s="5"/>
+      <c r="B548" s="6"/>
+      <c r="C548" s="5"/>
+    </row>
+    <row r="549">
+      <c r="A549" s="5"/>
+      <c r="B549" s="6"/>
+      <c r="C549" s="5"/>
+    </row>
+    <row r="550">
+      <c r="A550" s="5"/>
+      <c r="B550" s="6"/>
+      <c r="C550" s="5"/>
+    </row>
+    <row r="551">
+      <c r="A551" s="5"/>
+      <c r="B551" s="6"/>
+      <c r="C551" s="5"/>
+    </row>
+    <row r="552">
+      <c r="A552" s="5"/>
+      <c r="B552" s="6"/>
+      <c r="C552" s="5"/>
+    </row>
+    <row r="553">
+      <c r="A553" s="5"/>
+      <c r="B553" s="6"/>
+      <c r="C553" s="5"/>
+    </row>
+    <row r="554">
+      <c r="A554" s="5"/>
+      <c r="B554" s="6"/>
+      <c r="C554" s="5"/>
+    </row>
+    <row r="555">
+      <c r="A555" s="5"/>
+      <c r="B555" s="6"/>
+      <c r="C555" s="5"/>
+    </row>
+    <row r="556">
+      <c r="A556" s="5"/>
+      <c r="B556" s="6"/>
+      <c r="C556" s="5"/>
+    </row>
+    <row r="557">
+      <c r="A557" s="5"/>
+      <c r="B557" s="6"/>
+      <c r="C557" s="5"/>
+    </row>
+    <row r="558">
+      <c r="A558" s="5"/>
+      <c r="B558" s="6"/>
+      <c r="C558" s="5"/>
+    </row>
+    <row r="559">
+      <c r="A559" s="5"/>
+      <c r="B559" s="6"/>
+      <c r="C559" s="5"/>
+    </row>
+    <row r="560">
+      <c r="A560" s="5"/>
+      <c r="B560" s="6"/>
+      <c r="C560" s="5"/>
+    </row>
+    <row r="561">
+      <c r="A561" s="5"/>
+      <c r="B561" s="6"/>
+      <c r="C561" s="5"/>
+    </row>
+    <row r="562">
+      <c r="A562" s="5"/>
+      <c r="B562" s="6"/>
+      <c r="C562" s="5"/>
+    </row>
+    <row r="563">
+      <c r="A563" s="5"/>
+      <c r="B563" s="6"/>
+      <c r="C563" s="5"/>
+    </row>
+    <row r="564">
+      <c r="A564" s="5"/>
+      <c r="B564" s="6"/>
+      <c r="C564" s="5"/>
+    </row>
+    <row r="565">
+      <c r="A565" s="5"/>
+      <c r="B565" s="6"/>
+      <c r="C565" s="5"/>
+    </row>
+    <row r="566">
+      <c r="A566" s="5"/>
+      <c r="B566" s="6"/>
+      <c r="C566" s="5"/>
+    </row>
+    <row r="567">
+      <c r="A567" s="5"/>
+      <c r="B567" s="6"/>
+      <c r="C567" s="5"/>
+    </row>
+    <row r="568">
+      <c r="A568" s="5"/>
+      <c r="B568" s="6"/>
+      <c r="C568" s="5"/>
+    </row>
+    <row r="569">
+      <c r="A569" s="5"/>
+      <c r="B569" s="6"/>
+      <c r="C569" s="5"/>
+    </row>
+    <row r="570">
+      <c r="A570" s="5"/>
+      <c r="B570" s="6"/>
+      <c r="C570" s="5"/>
+    </row>
+    <row r="571">
+      <c r="A571" s="5"/>
+      <c r="B571" s="6"/>
+      <c r="C571" s="5"/>
+    </row>
+    <row r="572">
+      <c r="A572" s="5"/>
+      <c r="B572" s="6"/>
+      <c r="C572" s="5"/>
+    </row>
+    <row r="573">
+      <c r="A573" s="5"/>
+      <c r="B573" s="6"/>
+      <c r="C573" s="5"/>
+    </row>
+    <row r="574">
+      <c r="A574" s="5"/>
+      <c r="B574" s="6"/>
+      <c r="C574" s="5"/>
+    </row>
+    <row r="575">
+      <c r="A575" s="5"/>
+      <c r="B575" s="6"/>
+      <c r="C575" s="5"/>
+    </row>
+    <row r="576">
+      <c r="A576" s="5"/>
+      <c r="B576" s="6"/>
+      <c r="C576" s="5"/>
+    </row>
+    <row r="577">
+      <c r="A577" s="5"/>
+      <c r="B577" s="6"/>
+      <c r="C577" s="5"/>
+    </row>
+    <row r="578">
+      <c r="A578" s="5"/>
+      <c r="B578" s="6"/>
+      <c r="C578" s="5"/>
+    </row>
+    <row r="579">
+      <c r="A579" s="5"/>
+      <c r="B579" s="6"/>
+      <c r="C579" s="5"/>
+    </row>
+    <row r="580">
+      <c r="A580" s="5"/>
+      <c r="B580" s="6"/>
+      <c r="C580" s="5"/>
+    </row>
+    <row r="581">
+      <c r="A581" s="5"/>
+      <c r="B581" s="6"/>
+      <c r="C581" s="5"/>
+    </row>
+    <row r="582">
+      <c r="A582" s="5"/>
+      <c r="B582" s="6"/>
+      <c r="C582" s="5"/>
+    </row>
+    <row r="583">
+      <c r="A583" s="5"/>
+      <c r="B583" s="6"/>
+      <c r="C583" s="5"/>
+    </row>
+    <row r="584">
+      <c r="A584" s="5"/>
+      <c r="B584" s="6"/>
+      <c r="C584" s="5"/>
+    </row>
+    <row r="585">
+      <c r="A585" s="5"/>
+      <c r="B585" s="6"/>
+      <c r="C585" s="5"/>
+    </row>
+    <row r="586">
+      <c r="A586" s="5"/>
+      <c r="B586" s="6"/>
+      <c r="C586" s="5"/>
+    </row>
+    <row r="587">
+      <c r="A587" s="5"/>
+      <c r="B587" s="6"/>
+      <c r="C587" s="5"/>
+    </row>
+    <row r="588">
+      <c r="A588" s="5"/>
+      <c r="B588" s="6"/>
+      <c r="C588" s="5"/>
+    </row>
+    <row r="589">
+      <c r="A589" s="5"/>
+      <c r="B589" s="6"/>
+      <c r="C589" s="5"/>
+    </row>
+    <row r="590">
+      <c r="A590" s="5"/>
+      <c r="B590" s="6"/>
+      <c r="C590" s="5"/>
+    </row>
+    <row r="591">
+      <c r="A591" s="5"/>
+      <c r="B591" s="6"/>
+      <c r="C591" s="5"/>
+    </row>
+    <row r="592">
+      <c r="A592" s="5"/>
+      <c r="B592" s="6"/>
+      <c r="C592" s="5"/>
+    </row>
+    <row r="593">
+      <c r="A593" s="5"/>
+      <c r="B593" s="6"/>
+      <c r="C593" s="5"/>
+    </row>
+    <row r="594">
+      <c r="A594" s="5"/>
+      <c r="B594" s="6"/>
+      <c r="C594" s="5"/>
+    </row>
+    <row r="595">
+      <c r="A595" s="5"/>
+      <c r="B595" s="6"/>
+      <c r="C595" s="5"/>
+    </row>
+    <row r="596">
+      <c r="A596" s="5"/>
+      <c r="B596" s="6"/>
+      <c r="C596" s="5"/>
+    </row>
+    <row r="597">
+      <c r="A597" s="5"/>
+      <c r="B597" s="6"/>
+      <c r="C597" s="5"/>
+    </row>
+    <row r="598">
+      <c r="A598" s="5"/>
+      <c r="B598" s="6"/>
+      <c r="C598" s="5"/>
+    </row>
+    <row r="599">
+      <c r="A599" s="5"/>
+      <c r="B599" s="6"/>
+      <c r="C599" s="5"/>
+    </row>
+    <row r="600">
+      <c r="A600" s="5"/>
+      <c r="B600" s="6"/>
+      <c r="C600" s="5"/>
+    </row>
+    <row r="601">
+      <c r="A601" s="5"/>
+      <c r="B601" s="6"/>
+      <c r="C601" s="5"/>
+    </row>
+    <row r="602">
+      <c r="A602" s="5"/>
+      <c r="B602" s="6"/>
+      <c r="C602" s="5"/>
+    </row>
+    <row r="603">
+      <c r="A603" s="5"/>
+      <c r="B603" s="6"/>
+      <c r="C603" s="5"/>
+    </row>
+    <row r="604">
+      <c r="A604" s="5"/>
+      <c r="B604" s="6"/>
+      <c r="C604" s="5"/>
+    </row>
+    <row r="605">
+      <c r="A605" s="5"/>
+      <c r="B605" s="6"/>
+      <c r="C605" s="5"/>
+    </row>
+    <row r="606">
+      <c r="A606" s="5"/>
+      <c r="B606" s="6"/>
+      <c r="C606" s="5"/>
+    </row>
+    <row r="607">
+      <c r="A607" s="5"/>
+      <c r="B607" s="6"/>
+      <c r="C607" s="5"/>
+    </row>
+    <row r="608">
+      <c r="A608" s="5"/>
+      <c r="B608" s="6"/>
+      <c r="C608" s="5"/>
+    </row>
+    <row r="609">
+      <c r="A609" s="5"/>
+      <c r="B609" s="6"/>
+      <c r="C609" s="5"/>
+    </row>
+    <row r="610">
+      <c r="A610" s="5"/>
+      <c r="B610" s="6"/>
+      <c r="C610" s="5"/>
+    </row>
+    <row r="611">
+      <c r="A611" s="5"/>
+      <c r="B611" s="6"/>
+      <c r="C611" s="5"/>
+    </row>
+    <row r="612">
+      <c r="A612" s="5"/>
+      <c r="B612" s="6"/>
+      <c r="C612" s="5"/>
+    </row>
+    <row r="613">
+      <c r="A613" s="5"/>
+      <c r="B613" s="6"/>
+      <c r="C613" s="5"/>
+    </row>
+    <row r="614">
+      <c r="A614" s="5"/>
+      <c r="B614" s="6"/>
+      <c r="C614" s="5"/>
+    </row>
+    <row r="615">
+      <c r="A615" s="5"/>
+      <c r="B615" s="6"/>
+      <c r="C615" s="5"/>
+    </row>
+    <row r="616">
+      <c r="A616" s="5"/>
+      <c r="B616" s="6"/>
+      <c r="C616" s="5"/>
+    </row>
+    <row r="617">
+      <c r="A617" s="5"/>
+      <c r="B617" s="6"/>
+      <c r="C617" s="5"/>
+    </row>
+    <row r="618">
+      <c r="A618" s="5"/>
+      <c r="B618" s="6"/>
+      <c r="C618" s="5"/>
+    </row>
+    <row r="619">
+      <c r="A619" s="5"/>
+      <c r="B619" s="6"/>
+      <c r="C619" s="5"/>
+    </row>
+    <row r="620">
+      <c r="A620" s="5"/>
+      <c r="B620" s="6"/>
+      <c r="C620" s="5"/>
+    </row>
+    <row r="621">
+      <c r="A621" s="5"/>
+      <c r="B621" s="6"/>
+      <c r="C621" s="5"/>
+    </row>
+    <row r="622">
+      <c r="A622" s="5"/>
+      <c r="B622" s="6"/>
+      <c r="C622" s="5"/>
+    </row>
+    <row r="623">
+      <c r="A623" s="5"/>
+      <c r="B623" s="6"/>
+      <c r="C623" s="5"/>
+    </row>
+    <row r="624">
+      <c r="A624" s="5"/>
+      <c r="B624" s="6"/>
+      <c r="C624" s="5"/>
+    </row>
+    <row r="625">
+      <c r="A625" s="5"/>
+      <c r="B625" s="6"/>
+      <c r="C625" s="5"/>
+    </row>
+    <row r="626">
+      <c r="A626" s="5"/>
+      <c r="B626" s="6"/>
+      <c r="C626" s="5"/>
+    </row>
+    <row r="627">
+      <c r="A627" s="5"/>
+      <c r="B627" s="6"/>
+      <c r="C627" s="5"/>
+    </row>
+    <row r="628">
+      <c r="A628" s="5"/>
+      <c r="B628" s="6"/>
+      <c r="C628" s="5"/>
+    </row>
+    <row r="629">
+      <c r="A629" s="5"/>
+      <c r="B629" s="6"/>
+      <c r="C629" s="5"/>
+    </row>
+    <row r="630">
+      <c r="A630" s="5"/>
+      <c r="B630" s="6"/>
+      <c r="C630" s="5"/>
+    </row>
+    <row r="631">
+      <c r="A631" s="5"/>
+      <c r="B631" s="6"/>
+      <c r="C631" s="5"/>
+    </row>
+    <row r="632">
+      <c r="A632" s="5"/>
+      <c r="B632" s="6"/>
+      <c r="C632" s="5"/>
+    </row>
+    <row r="633">
+      <c r="A633" s="5"/>
+      <c r="B633" s="6"/>
+      <c r="C633" s="5"/>
+    </row>
+    <row r="634">
+      <c r="A634" s="5"/>
+      <c r="B634" s="6"/>
+      <c r="C634" s="5"/>
+    </row>
+    <row r="635">
+      <c r="A635" s="5"/>
+      <c r="B635" s="6"/>
+      <c r="C635" s="5"/>
+    </row>
+    <row r="636">
+      <c r="A636" s="5"/>
+      <c r="B636" s="6"/>
+      <c r="C636" s="5"/>
+    </row>
+    <row r="637">
+      <c r="A637" s="5"/>
+      <c r="B637" s="6"/>
+      <c r="C637" s="5"/>
+    </row>
+    <row r="638">
+      <c r="A638" s="5"/>
+      <c r="B638" s="6"/>
+      <c r="C638" s="5"/>
+    </row>
+    <row r="639">
+      <c r="A639" s="5"/>
+      <c r="B639" s="6"/>
+      <c r="C639" s="5"/>
+    </row>
+    <row r="640">
+      <c r="A640" s="5"/>
+      <c r="B640" s="6"/>
+      <c r="C640" s="5"/>
+    </row>
+    <row r="641">
+      <c r="A641" s="5"/>
+      <c r="B641" s="6"/>
+      <c r="C641" s="5"/>
+    </row>
+    <row r="642">
+      <c r="A642" s="5"/>
+      <c r="B642" s="6"/>
+      <c r="C642" s="5"/>
+    </row>
+    <row r="643">
+      <c r="A643" s="5"/>
+      <c r="B643" s="6"/>
+      <c r="C643" s="5"/>
+    </row>
+    <row r="644">
+      <c r="A644" s="5"/>
+      <c r="B644" s="6"/>
+      <c r="C644" s="5"/>
+    </row>
+    <row r="645">
+      <c r="A645" s="5"/>
+      <c r="B645" s="6"/>
+      <c r="C645" s="5"/>
+    </row>
+    <row r="646">
+      <c r="A646" s="5"/>
+      <c r="B646" s="6"/>
+      <c r="C646" s="5"/>
+    </row>
+    <row r="647">
+      <c r="A647" s="5"/>
+      <c r="B647" s="6"/>
+      <c r="C647" s="5"/>
+    </row>
+    <row r="648">
+      <c r="A648" s="5"/>
+      <c r="B648" s="6"/>
+      <c r="C648" s="5"/>
+    </row>
+    <row r="649">
+      <c r="A649" s="5"/>
+      <c r="B649" s="6"/>
+      <c r="C649" s="5"/>
+    </row>
+    <row r="650">
+      <c r="A650" s="5"/>
+      <c r="B650" s="6"/>
+      <c r="C650" s="5"/>
+    </row>
+    <row r="651">
+      <c r="A651" s="5"/>
+      <c r="B651" s="6"/>
+      <c r="C651" s="5"/>
+    </row>
+    <row r="652">
+      <c r="A652" s="5"/>
+      <c r="B652" s="6"/>
+      <c r="C652" s="5"/>
+    </row>
+    <row r="653">
+      <c r="A653" s="5"/>
+      <c r="B653" s="6"/>
+      <c r="C653" s="5"/>
+    </row>
+    <row r="654">
+      <c r="A654" s="5"/>
+      <c r="B654" s="6"/>
+      <c r="C654" s="5"/>
+    </row>
+    <row r="655">
+      <c r="A655" s="5"/>
+      <c r="B655" s="6"/>
+      <c r="C655" s="5"/>
+    </row>
+    <row r="656">
+      <c r="A656" s="5"/>
+      <c r="B656" s="6"/>
+      <c r="C656" s="5"/>
+    </row>
+    <row r="657">
+      <c r="A657" s="5"/>
+      <c r="B657" s="6"/>
+      <c r="C657" s="5"/>
+    </row>
+    <row r="658">
+      <c r="A658" s="5"/>
+      <c r="B658" s="6"/>
+      <c r="C658" s="5"/>
+    </row>
+    <row r="659">
+      <c r="A659" s="5"/>
+      <c r="B659" s="6"/>
+      <c r="C659" s="5"/>
+    </row>
+    <row r="660">
+      <c r="A660" s="5"/>
+      <c r="B660" s="6"/>
+      <c r="C660" s="5"/>
+    </row>
+    <row r="661">
+      <c r="A661" s="5"/>
+      <c r="B661" s="6"/>
+      <c r="C661" s="5"/>
+    </row>
+    <row r="662">
+      <c r="A662" s="5"/>
+      <c r="B662" s="6"/>
+      <c r="C662" s="5"/>
+    </row>
+    <row r="663">
+      <c r="A663" s="5"/>
+      <c r="B663" s="6"/>
+      <c r="C663" s="5"/>
+    </row>
+    <row r="664">
+      <c r="A664" s="5"/>
+      <c r="B664" s="6"/>
+      <c r="C664" s="5"/>
+    </row>
+    <row r="665">
+      <c r="A665" s="5"/>
+      <c r="B665" s="6"/>
+      <c r="C665" s="5"/>
+    </row>
+    <row r="666">
+      <c r="A666" s="5"/>
+      <c r="B666" s="6"/>
+      <c r="C666" s="5"/>
+    </row>
+    <row r="667">
+      <c r="A667" s="5"/>
+      <c r="B667" s="6"/>
+      <c r="C667" s="5"/>
+    </row>
+    <row r="668">
+      <c r="A668" s="5"/>
+      <c r="B668" s="6"/>
+      <c r="C668" s="5"/>
+    </row>
+    <row r="669">
+      <c r="A669" s="5"/>
+      <c r="B669" s="6"/>
+      <c r="C669" s="5"/>
+    </row>
+    <row r="670">
+      <c r="A670" s="5"/>
+      <c r="B670" s="6"/>
+      <c r="C670" s="5"/>
+    </row>
+    <row r="671">
+      <c r="A671" s="5"/>
+      <c r="B671" s="6"/>
+      <c r="C671" s="5"/>
+    </row>
+    <row r="672">
+      <c r="A672" s="5"/>
+      <c r="B672" s="6"/>
+      <c r="C672" s="5"/>
+    </row>
+    <row r="673">
+      <c r="A673" s="5"/>
+      <c r="B673" s="6"/>
+      <c r="C673" s="5"/>
+    </row>
+    <row r="674">
+      <c r="A674" s="5"/>
+      <c r="B674" s="6"/>
+      <c r="C674" s="5"/>
+    </row>
+    <row r="675">
+      <c r="A675" s="5"/>
+      <c r="B675" s="6"/>
+      <c r="C675" s="5"/>
+    </row>
+    <row r="676">
+      <c r="A676" s="5"/>
+      <c r="B676" s="6"/>
+      <c r="C676" s="5"/>
+    </row>
+    <row r="677">
+      <c r="A677" s="5"/>
+      <c r="B677" s="6"/>
+      <c r="C677" s="5"/>
+    </row>
+    <row r="678">
+      <c r="A678" s="5"/>
+      <c r="B678" s="6"/>
+      <c r="C678" s="5"/>
+    </row>
+    <row r="679">
+      <c r="A679" s="5"/>
+      <c r="B679" s="6"/>
+      <c r="C679" s="5"/>
+    </row>
+    <row r="680">
+      <c r="A680" s="5"/>
+      <c r="B680" s="6"/>
+      <c r="C680" s="5"/>
+    </row>
+    <row r="681">
+      <c r="A681" s="5"/>
+      <c r="B681" s="6"/>
+      <c r="C681" s="5"/>
+    </row>
+    <row r="682">
+      <c r="A682" s="5"/>
+      <c r="B682" s="6"/>
+      <c r="C682" s="5"/>
+    </row>
+    <row r="683">
+      <c r="A683" s="5"/>
+      <c r="B683" s="6"/>
+      <c r="C683" s="5"/>
+    </row>
+    <row r="684">
+      <c r="A684" s="5"/>
+      <c r="B684" s="6"/>
+      <c r="C684" s="5"/>
+    </row>
+    <row r="685">
+      <c r="A685" s="5"/>
+      <c r="B685" s="6"/>
+      <c r="C685" s="5"/>
+    </row>
+    <row r="686">
+      <c r="A686" s="5"/>
+      <c r="B686" s="6"/>
+      <c r="C686" s="5"/>
+    </row>
+    <row r="687">
+      <c r="A687" s="5"/>
+      <c r="B687" s="6"/>
+      <c r="C687" s="5"/>
+    </row>
+    <row r="688">
+      <c r="A688" s="5"/>
+      <c r="B688" s="6"/>
+      <c r="C688" s="5"/>
+    </row>
+    <row r="689">
+      <c r="A689" s="5"/>
+      <c r="B689" s="6"/>
+      <c r="C689" s="5"/>
+    </row>
+    <row r="690">
+      <c r="A690" s="5"/>
+      <c r="B690" s="6"/>
+      <c r="C690" s="5"/>
+    </row>
+    <row r="691">
+      <c r="A691" s="5"/>
+      <c r="B691" s="6"/>
+      <c r="C691" s="5"/>
+    </row>
+    <row r="692">
+      <c r="A692" s="5"/>
+      <c r="B692" s="6"/>
+      <c r="C692" s="5"/>
+    </row>
+    <row r="693">
+      <c r="A693" s="5"/>
+      <c r="B693" s="6"/>
+      <c r="C693" s="5"/>
+    </row>
+    <row r="694">
+      <c r="A694" s="5"/>
+      <c r="B694" s="6"/>
+      <c r="C694" s="5"/>
+    </row>
+    <row r="695">
+      <c r="A695" s="5"/>
+      <c r="B695" s="6"/>
+      <c r="C695" s="5"/>
+    </row>
+    <row r="696">
+      <c r="A696" s="5"/>
+      <c r="B696" s="6"/>
+      <c r="C696" s="5"/>
+    </row>
+    <row r="697">
+      <c r="A697" s="5"/>
+      <c r="B697" s="6"/>
+      <c r="C697" s="5"/>
+    </row>
+    <row r="698">
+      <c r="A698" s="5"/>
+      <c r="B698" s="6"/>
+      <c r="C698" s="5"/>
+    </row>
+    <row r="699">
+      <c r="A699" s="5"/>
+      <c r="B699" s="6"/>
+      <c r="C699" s="5"/>
+    </row>
+    <row r="700">
+      <c r="A700" s="5"/>
+      <c r="B700" s="6"/>
+      <c r="C700" s="5"/>
+    </row>
+    <row r="701">
+      <c r="A701" s="5"/>
+      <c r="B701" s="6"/>
+      <c r="C701" s="5"/>
+    </row>
+    <row r="702">
+      <c r="A702" s="5"/>
+      <c r="B702" s="6"/>
+      <c r="C702" s="5"/>
+    </row>
+    <row r="703">
+      <c r="A703" s="5"/>
+      <c r="B703" s="6"/>
+      <c r="C703" s="5"/>
+    </row>
+    <row r="704">
+      <c r="A704" s="5"/>
+      <c r="B704" s="6"/>
+      <c r="C704" s="5"/>
+    </row>
+    <row r="705">
+      <c r="A705" s="5"/>
+      <c r="B705" s="6"/>
+      <c r="C705" s="5"/>
+    </row>
+    <row r="706">
+      <c r="A706" s="5"/>
+      <c r="B706" s="6"/>
+      <c r="C706" s="5"/>
+    </row>
+    <row r="707">
+      <c r="A707" s="5"/>
+      <c r="B707" s="6"/>
+      <c r="C707" s="5"/>
+    </row>
+    <row r="708">
+      <c r="A708" s="5"/>
+      <c r="B708" s="6"/>
+      <c r="C708" s="5"/>
+    </row>
+    <row r="709">
+      <c r="A709" s="5"/>
+      <c r="B709" s="6"/>
+      <c r="C709" s="5"/>
+    </row>
+    <row r="710">
+      <c r="A710" s="5"/>
+      <c r="B710" s="6"/>
+      <c r="C710" s="5"/>
+    </row>
+    <row r="711">
+      <c r="A711" s="5"/>
+      <c r="B711" s="6"/>
+      <c r="C711" s="5"/>
+    </row>
+    <row r="712">
+      <c r="A712" s="5"/>
+      <c r="B712" s="6"/>
+      <c r="C712" s="5"/>
+    </row>
+    <row r="713">
+      <c r="A713" s="5"/>
+      <c r="B713" s="6"/>
+      <c r="C713" s="5"/>
+    </row>
+    <row r="714">
+      <c r="A714" s="5"/>
+      <c r="B714" s="6"/>
+      <c r="C714" s="5"/>
+    </row>
+    <row r="715">
+      <c r="A715" s="5"/>
+      <c r="B715" s="6"/>
+      <c r="C715" s="5"/>
+    </row>
+    <row r="716">
+      <c r="A716" s="5"/>
+      <c r="B716" s="6"/>
+      <c r="C716" s="5"/>
+    </row>
+    <row r="717">
+      <c r="A717" s="5"/>
+      <c r="B717" s="6"/>
+      <c r="C717" s="5"/>
+    </row>
+    <row r="718">
+      <c r="A718" s="5"/>
+      <c r="B718" s="6"/>
+      <c r="C718" s="5"/>
+    </row>
+    <row r="719">
+      <c r="A719" s="5"/>
+      <c r="B719" s="6"/>
+      <c r="C719" s="5"/>
+    </row>
+    <row r="720">
+      <c r="A720" s="5"/>
+      <c r="B720" s="6"/>
+      <c r="C720" s="5"/>
+    </row>
+    <row r="721">
+      <c r="A721" s="5"/>
+      <c r="B721" s="6"/>
+      <c r="C721" s="5"/>
+    </row>
+    <row r="722">
+      <c r="A722" s="5"/>
+      <c r="B722" s="6"/>
+      <c r="C722" s="5"/>
+    </row>
+    <row r="723">
+      <c r="A723" s="5"/>
+      <c r="B723" s="6"/>
+      <c r="C723" s="5"/>
+    </row>
+    <row r="724">
+      <c r="A724" s="5"/>
+      <c r="B724" s="6"/>
+      <c r="C724" s="5"/>
+    </row>
+    <row r="725">
+      <c r="A725" s="5"/>
+      <c r="B725" s="6"/>
+      <c r="C725" s="5"/>
+    </row>
+    <row r="726">
+      <c r="A726" s="5"/>
+      <c r="B726" s="6"/>
+      <c r="C726" s="5"/>
+    </row>
+    <row r="727">
+      <c r="A727" s="5"/>
+      <c r="B727" s="6"/>
+      <c r="C727" s="5"/>
+    </row>
+    <row r="728">
+      <c r="A728" s="5"/>
+      <c r="B728" s="6"/>
+      <c r="C728" s="5"/>
+    </row>
+    <row r="729">
+      <c r="A729" s="5"/>
+      <c r="B729" s="6"/>
+      <c r="C729" s="5"/>
+    </row>
+    <row r="730">
+      <c r="A730" s="5"/>
+      <c r="B730" s="6"/>
+      <c r="C730" s="5"/>
+    </row>
+    <row r="731">
+      <c r="A731" s="5"/>
+      <c r="B731" s="6"/>
+      <c r="C731" s="5"/>
+    </row>
+    <row r="732">
+      <c r="A732" s="5"/>
+      <c r="B732" s="6"/>
+      <c r="C732" s="5"/>
+    </row>
+    <row r="733">
+      <c r="A733" s="5"/>
+      <c r="B733" s="6"/>
+      <c r="C733" s="5"/>
+    </row>
+    <row r="734">
+      <c r="A734" s="5"/>
+      <c r="B734" s="6"/>
+      <c r="C734" s="5"/>
+    </row>
+    <row r="735">
+      <c r="A735" s="5"/>
+      <c r="B735" s="6"/>
+      <c r="C735" s="5"/>
+    </row>
+    <row r="736">
+      <c r="A736" s="5"/>
+      <c r="B736" s="6"/>
+      <c r="C736" s="5"/>
+    </row>
+    <row r="737">
+      <c r="A737" s="5"/>
+      <c r="B737" s="6"/>
+      <c r="C737" s="5"/>
+    </row>
+    <row r="738">
+      <c r="A738" s="5"/>
+      <c r="B738" s="6"/>
+      <c r="C738" s="5"/>
+    </row>
+    <row r="739">
+      <c r="A739" s="5"/>
+      <c r="B739" s="6"/>
+      <c r="C739" s="5"/>
+    </row>
+    <row r="740">
+      <c r="A740" s="5"/>
+      <c r="B740" s="6"/>
+      <c r="C740" s="5"/>
+    </row>
+    <row r="741">
+      <c r="A741" s="5"/>
+      <c r="B741" s="6"/>
+      <c r="C741" s="5"/>
+    </row>
+    <row r="742">
+      <c r="A742" s="5"/>
+      <c r="B742" s="6"/>
+      <c r="C742" s="5"/>
+    </row>
+    <row r="743">
+      <c r="A743" s="5"/>
+      <c r="B743" s="6"/>
+      <c r="C743" s="5"/>
+    </row>
+    <row r="744">
+      <c r="A744" s="5"/>
+      <c r="B744" s="6"/>
+      <c r="C744" s="5"/>
+    </row>
+    <row r="745">
+      <c r="A745" s="5"/>
+      <c r="B745" s="6"/>
+      <c r="C745" s="5"/>
+    </row>
+    <row r="746">
+      <c r="A746" s="5"/>
+      <c r="B746" s="6"/>
+      <c r="C746" s="5"/>
+    </row>
+    <row r="747">
+      <c r="A747" s="5"/>
+      <c r="B747" s="6"/>
+      <c r="C747" s="5"/>
+    </row>
+    <row r="748">
+      <c r="A748" s="5"/>
+      <c r="B748" s="6"/>
+      <c r="C748" s="5"/>
+    </row>
+    <row r="749">
+      <c r="A749" s="5"/>
+      <c r="B749" s="6"/>
+      <c r="C749" s="5"/>
+    </row>
+    <row r="750">
+      <c r="A750" s="5"/>
+      <c r="B750" s="6"/>
+      <c r="C750" s="5"/>
+    </row>
+    <row r="751">
+      <c r="A751" s="5"/>
+      <c r="B751" s="6"/>
+      <c r="C751" s="5"/>
+    </row>
+    <row r="752">
+      <c r="A752" s="5"/>
+      <c r="B752" s="6"/>
+      <c r="C752" s="5"/>
+    </row>
+    <row r="753">
+      <c r="A753" s="5"/>
+      <c r="B753" s="6"/>
+      <c r="C753" s="5"/>
+    </row>
+    <row r="754">
+      <c r="A754" s="5"/>
+      <c r="B754" s="6"/>
+      <c r="C754" s="5"/>
+    </row>
+    <row r="755">
+      <c r="A755" s="5"/>
+      <c r="B755" s="6"/>
+      <c r="C755" s="5"/>
+    </row>
+    <row r="756">
+      <c r="A756" s="5"/>
+      <c r="B756" s="6"/>
+      <c r="C756" s="5"/>
+    </row>
+    <row r="757">
+      <c r="A757" s="5"/>
+      <c r="B757" s="6"/>
+      <c r="C757" s="5"/>
+    </row>
+    <row r="758">
+      <c r="A758" s="5"/>
+      <c r="B758" s="6"/>
+      <c r="C758" s="5"/>
+    </row>
+    <row r="759">
+      <c r="A759" s="5"/>
+      <c r="B759" s="6"/>
+      <c r="C759" s="5"/>
+    </row>
+    <row r="760">
+      <c r="A760" s="5"/>
+      <c r="B760" s="6"/>
+      <c r="C760" s="5"/>
+    </row>
+    <row r="761">
+      <c r="A761" s="5"/>
+      <c r="B761" s="6"/>
+      <c r="C761" s="5"/>
+    </row>
+    <row r="762">
+      <c r="A762" s="5"/>
+      <c r="B762" s="6"/>
+      <c r="C762" s="5"/>
+    </row>
+    <row r="763">
+      <c r="A763" s="5"/>
+      <c r="B763" s="6"/>
+      <c r="C763" s="5"/>
+    </row>
+    <row r="764">
+      <c r="A764" s="5"/>
+      <c r="B764" s="6"/>
+      <c r="C764" s="5"/>
+    </row>
+    <row r="765">
+      <c r="A765" s="5"/>
+      <c r="B765" s="6"/>
+      <c r="C765" s="5"/>
+    </row>
+    <row r="766">
+      <c r="A766" s="5"/>
+      <c r="B766" s="6"/>
+      <c r="C766" s="5"/>
+    </row>
+    <row r="767">
+      <c r="A767" s="5"/>
+      <c r="B767" s="6"/>
+      <c r="C767" s="5"/>
+    </row>
+    <row r="768">
+      <c r="A768" s="5"/>
+      <c r="B768" s="6"/>
+      <c r="C768" s="5"/>
+    </row>
+    <row r="769">
+      <c r="A769" s="5"/>
+      <c r="B769" s="6"/>
+      <c r="C769" s="5"/>
+    </row>
+    <row r="770">
+      <c r="A770" s="5"/>
+      <c r="B770" s="6"/>
+      <c r="C770" s="5"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E470"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" sqref="A2:A870">
+      <formula1>"2ЭС5К,3ЭС5К,4ЭС5К"</formula1>
+    </dataValidation>
+  </dataValidations>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E526"/>

--- a/zona_riska.xlsx
+++ b/zona_riska.xlsx
@@ -23,6 +23,7 @@
     <sheet name="Пробег" sheetId="9" r:id="rId9"/>
     <sheet name="Места осмотра" sheetId="10" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Тест" sheetId="11" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="РТ-130" sheetId="12" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">БИ!$A$1:$E$441</definedName>
@@ -13679,6 +13680,1555 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="4" max="4" width="36" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Серия</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Номер</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Приписка</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Место осмотра (необязательно)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Комментарий (необязательно)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="5"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="5"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="5"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="5"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="5"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="5"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="5"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="5"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="5"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="5"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="5"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="5"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="5"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="5"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="5"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="5"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="5"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="5"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="5"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="5"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="5"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="5"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="5"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="5"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="5"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="5"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="5"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="5"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="5"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="5"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="5"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="5"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="5"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="5"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="5"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="5"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="5"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="5"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="5"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="5"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="5"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="5"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="5"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="5"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5"/>
+      <c r="B46" s="6"/>
+      <c r="C46" s="5"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5"/>
+      <c r="B47" s="6"/>
+      <c r="C47" s="5"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="5"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="5"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="5"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="5"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5"/>
+      <c r="B52" s="6"/>
+      <c r="C52" s="5"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5"/>
+      <c r="B53" s="6"/>
+      <c r="C53" s="5"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5"/>
+      <c r="B54" s="6"/>
+      <c r="C54" s="5"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5"/>
+      <c r="B55" s="6"/>
+      <c r="C55" s="5"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5"/>
+      <c r="B56" s="6"/>
+      <c r="C56" s="5"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5"/>
+      <c r="B57" s="6"/>
+      <c r="C57" s="5"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="5"/>
+      <c r="B58" s="6"/>
+      <c r="C58" s="5"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="5"/>
+      <c r="B59" s="6"/>
+      <c r="C59" s="5"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="5"/>
+      <c r="B60" s="6"/>
+      <c r="C60" s="5"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="5"/>
+      <c r="B61" s="6"/>
+      <c r="C61" s="5"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="5"/>
+      <c r="B62" s="6"/>
+      <c r="C62" s="5"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="5"/>
+      <c r="B63" s="6"/>
+      <c r="C63" s="5"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5"/>
+      <c r="B64" s="6"/>
+      <c r="C64" s="5"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5"/>
+      <c r="B65" s="6"/>
+      <c r="C65" s="5"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="5"/>
+      <c r="B66" s="6"/>
+      <c r="C66" s="5"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5"/>
+      <c r="B67" s="6"/>
+      <c r="C67" s="5"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5"/>
+      <c r="B68" s="6"/>
+      <c r="C68" s="5"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5"/>
+      <c r="B69" s="6"/>
+      <c r="C69" s="5"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5"/>
+      <c r="B70" s="6"/>
+      <c r="C70" s="5"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="5"/>
+      <c r="B71" s="6"/>
+      <c r="C71" s="5"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="5"/>
+      <c r="B72" s="6"/>
+      <c r="C72" s="5"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="5"/>
+      <c r="B73" s="6"/>
+      <c r="C73" s="5"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="5"/>
+      <c r="B74" s="6"/>
+      <c r="C74" s="5"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="5"/>
+      <c r="B75" s="6"/>
+      <c r="C75" s="5"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="5"/>
+      <c r="B76" s="6"/>
+      <c r="C76" s="5"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="5"/>
+      <c r="B77" s="6"/>
+      <c r="C77" s="5"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="5"/>
+      <c r="B78" s="6"/>
+      <c r="C78" s="5"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="5"/>
+      <c r="B79" s="6"/>
+      <c r="C79" s="5"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="5"/>
+      <c r="B80" s="6"/>
+      <c r="C80" s="5"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="5"/>
+      <c r="B81" s="6"/>
+      <c r="C81" s="5"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="5"/>
+      <c r="B82" s="6"/>
+      <c r="C82" s="5"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="5"/>
+      <c r="B83" s="6"/>
+      <c r="C83" s="5"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="5"/>
+      <c r="B84" s="6"/>
+      <c r="C84" s="5"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="5"/>
+      <c r="B85" s="6"/>
+      <c r="C85" s="5"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="5"/>
+      <c r="B86" s="6"/>
+      <c r="C86" s="5"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="5"/>
+      <c r="B87" s="6"/>
+      <c r="C87" s="5"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="5"/>
+      <c r="B88" s="6"/>
+      <c r="C88" s="5"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="5"/>
+      <c r="B89" s="6"/>
+      <c r="C89" s="5"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="5"/>
+      <c r="B90" s="6"/>
+      <c r="C90" s="5"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="5"/>
+      <c r="B91" s="6"/>
+      <c r="C91" s="5"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="5"/>
+      <c r="B92" s="6"/>
+      <c r="C92" s="5"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="5"/>
+      <c r="B93" s="6"/>
+      <c r="C93" s="5"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="5"/>
+      <c r="B94" s="6"/>
+      <c r="C94" s="5"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="5"/>
+      <c r="B95" s="6"/>
+      <c r="C95" s="5"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="5"/>
+      <c r="B96" s="6"/>
+      <c r="C96" s="5"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="5"/>
+      <c r="B97" s="6"/>
+      <c r="C97" s="5"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="5"/>
+      <c r="B98" s="6"/>
+      <c r="C98" s="5"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="5"/>
+      <c r="B99" s="6"/>
+      <c r="C99" s="5"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="5"/>
+      <c r="B100" s="6"/>
+      <c r="C100" s="5"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="5"/>
+      <c r="B101" s="6"/>
+      <c r="C101" s="5"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="5"/>
+      <c r="B102" s="6"/>
+      <c r="C102" s="5"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="5"/>
+      <c r="B103" s="6"/>
+      <c r="C103" s="5"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="5"/>
+      <c r="B104" s="6"/>
+      <c r="C104" s="5"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="5"/>
+      <c r="B105" s="6"/>
+      <c r="C105" s="5"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="5"/>
+      <c r="B106" s="6"/>
+      <c r="C106" s="5"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="5"/>
+      <c r="B107" s="6"/>
+      <c r="C107" s="5"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="5"/>
+      <c r="B108" s="6"/>
+      <c r="C108" s="5"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="5"/>
+      <c r="B109" s="6"/>
+      <c r="C109" s="5"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="5"/>
+      <c r="B110" s="6"/>
+      <c r="C110" s="5"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="5"/>
+      <c r="B111" s="6"/>
+      <c r="C111" s="5"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="5"/>
+      <c r="B112" s="6"/>
+      <c r="C112" s="5"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="5"/>
+      <c r="B113" s="6"/>
+      <c r="C113" s="5"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="5"/>
+      <c r="B114" s="6"/>
+      <c r="C114" s="5"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="5"/>
+      <c r="B115" s="6"/>
+      <c r="C115" s="5"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="5"/>
+      <c r="B116" s="6"/>
+      <c r="C116" s="5"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="5"/>
+      <c r="B117" s="6"/>
+      <c r="C117" s="5"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="5"/>
+      <c r="B118" s="6"/>
+      <c r="C118" s="5"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="5"/>
+      <c r="B119" s="6"/>
+      <c r="C119" s="5"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="5"/>
+      <c r="B120" s="6"/>
+      <c r="C120" s="5"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="5"/>
+      <c r="B121" s="6"/>
+      <c r="C121" s="5"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="5"/>
+      <c r="B122" s="6"/>
+      <c r="C122" s="5"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="5"/>
+      <c r="B123" s="6"/>
+      <c r="C123" s="5"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="5"/>
+      <c r="B124" s="6"/>
+      <c r="C124" s="5"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="5"/>
+      <c r="B125" s="6"/>
+      <c r="C125" s="5"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="5"/>
+      <c r="B126" s="6"/>
+      <c r="C126" s="5"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="5"/>
+      <c r="B127" s="6"/>
+      <c r="C127" s="5"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="5"/>
+      <c r="B128" s="6"/>
+      <c r="C128" s="5"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="5"/>
+      <c r="B129" s="6"/>
+      <c r="C129" s="5"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="5"/>
+      <c r="B130" s="6"/>
+      <c r="C130" s="5"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="5"/>
+      <c r="B131" s="6"/>
+      <c r="C131" s="5"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="5"/>
+      <c r="B132" s="6"/>
+      <c r="C132" s="5"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="5"/>
+      <c r="B133" s="6"/>
+      <c r="C133" s="5"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="5"/>
+      <c r="B134" s="6"/>
+      <c r="C134" s="5"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="5"/>
+      <c r="B135" s="6"/>
+      <c r="C135" s="5"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="5"/>
+      <c r="B136" s="6"/>
+      <c r="C136" s="5"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="5"/>
+      <c r="B137" s="6"/>
+      <c r="C137" s="5"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="5"/>
+      <c r="B138" s="6"/>
+      <c r="C138" s="5"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="5"/>
+      <c r="B139" s="6"/>
+      <c r="C139" s="5"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="5"/>
+      <c r="B140" s="6"/>
+      <c r="C140" s="5"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="5"/>
+      <c r="B141" s="6"/>
+      <c r="C141" s="5"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="5"/>
+      <c r="B142" s="6"/>
+      <c r="C142" s="5"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="5"/>
+      <c r="B143" s="6"/>
+      <c r="C143" s="5"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="5"/>
+      <c r="B144" s="6"/>
+      <c r="C144" s="5"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="5"/>
+      <c r="B145" s="6"/>
+      <c r="C145" s="5"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="5"/>
+      <c r="B146" s="6"/>
+      <c r="C146" s="5"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="5"/>
+      <c r="B147" s="6"/>
+      <c r="C147" s="5"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="5"/>
+      <c r="B148" s="6"/>
+      <c r="C148" s="5"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="5"/>
+      <c r="B149" s="6"/>
+      <c r="C149" s="5"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="5"/>
+      <c r="B150" s="6"/>
+      <c r="C150" s="5"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="5"/>
+      <c r="B151" s="6"/>
+      <c r="C151" s="5"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="5"/>
+      <c r="B152" s="6"/>
+      <c r="C152" s="5"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="5"/>
+      <c r="B153" s="6"/>
+      <c r="C153" s="5"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="5"/>
+      <c r="B154" s="6"/>
+      <c r="C154" s="5"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="5"/>
+      <c r="B155" s="6"/>
+      <c r="C155" s="5"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="5"/>
+      <c r="B156" s="6"/>
+      <c r="C156" s="5"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="5"/>
+      <c r="B157" s="6"/>
+      <c r="C157" s="5"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="5"/>
+      <c r="B158" s="6"/>
+      <c r="C158" s="5"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="5"/>
+      <c r="B159" s="6"/>
+      <c r="C159" s="5"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="5"/>
+      <c r="B160" s="6"/>
+      <c r="C160" s="5"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="5"/>
+      <c r="B161" s="6"/>
+      <c r="C161" s="5"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="5"/>
+      <c r="B162" s="6"/>
+      <c r="C162" s="5"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="5"/>
+      <c r="B163" s="6"/>
+      <c r="C163" s="5"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="5"/>
+      <c r="B164" s="6"/>
+      <c r="C164" s="5"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="5"/>
+      <c r="B165" s="6"/>
+      <c r="C165" s="5"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="5"/>
+      <c r="B166" s="6"/>
+      <c r="C166" s="5"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="5"/>
+      <c r="B167" s="6"/>
+      <c r="C167" s="5"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="5"/>
+      <c r="B168" s="6"/>
+      <c r="C168" s="5"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="5"/>
+      <c r="B169" s="6"/>
+      <c r="C169" s="5"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="5"/>
+      <c r="B170" s="6"/>
+      <c r="C170" s="5"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="5"/>
+      <c r="B171" s="6"/>
+      <c r="C171" s="5"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="5"/>
+      <c r="B172" s="6"/>
+      <c r="C172" s="5"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="5"/>
+      <c r="B173" s="6"/>
+      <c r="C173" s="5"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="5"/>
+      <c r="B174" s="6"/>
+      <c r="C174" s="5"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="5"/>
+      <c r="B175" s="6"/>
+      <c r="C175" s="5"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="5"/>
+      <c r="B176" s="6"/>
+      <c r="C176" s="5"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="5"/>
+      <c r="B177" s="6"/>
+      <c r="C177" s="5"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="5"/>
+      <c r="B178" s="6"/>
+      <c r="C178" s="5"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="5"/>
+      <c r="B179" s="6"/>
+      <c r="C179" s="5"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="5"/>
+      <c r="B180" s="6"/>
+      <c r="C180" s="5"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="5"/>
+      <c r="B181" s="6"/>
+      <c r="C181" s="5"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="5"/>
+      <c r="B182" s="6"/>
+      <c r="C182" s="5"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="5"/>
+      <c r="B183" s="6"/>
+      <c r="C183" s="5"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="5"/>
+      <c r="B184" s="6"/>
+      <c r="C184" s="5"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="5"/>
+      <c r="B185" s="6"/>
+      <c r="C185" s="5"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="5"/>
+      <c r="B186" s="6"/>
+      <c r="C186" s="5"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="5"/>
+      <c r="B187" s="6"/>
+      <c r="C187" s="5"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="5"/>
+      <c r="B188" s="6"/>
+      <c r="C188" s="5"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="5"/>
+      <c r="B189" s="6"/>
+      <c r="C189" s="5"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="5"/>
+      <c r="B190" s="6"/>
+      <c r="C190" s="5"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="5"/>
+      <c r="B191" s="6"/>
+      <c r="C191" s="5"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="5"/>
+      <c r="B192" s="6"/>
+      <c r="C192" s="5"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="5"/>
+      <c r="B193" s="6"/>
+      <c r="C193" s="5"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="5"/>
+      <c r="B194" s="6"/>
+      <c r="C194" s="5"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="5"/>
+      <c r="B195" s="6"/>
+      <c r="C195" s="5"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="5"/>
+      <c r="B196" s="6"/>
+      <c r="C196" s="5"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="5"/>
+      <c r="B197" s="6"/>
+      <c r="C197" s="5"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="5"/>
+      <c r="B198" s="6"/>
+      <c r="C198" s="5"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="5"/>
+      <c r="B199" s="6"/>
+      <c r="C199" s="5"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="5"/>
+      <c r="B200" s="6"/>
+      <c r="C200" s="5"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="5"/>
+      <c r="B201" s="6"/>
+      <c r="C201" s="5"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="5"/>
+      <c r="B202" s="6"/>
+      <c r="C202" s="5"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="5"/>
+      <c r="B203" s="6"/>
+      <c r="C203" s="5"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="5"/>
+      <c r="B204" s="6"/>
+      <c r="C204" s="5"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="5"/>
+      <c r="B205" s="6"/>
+      <c r="C205" s="5"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="5"/>
+      <c r="B206" s="6"/>
+      <c r="C206" s="5"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="5"/>
+      <c r="B207" s="6"/>
+      <c r="C207" s="5"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="5"/>
+      <c r="B208" s="6"/>
+      <c r="C208" s="5"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="5"/>
+      <c r="B209" s="6"/>
+      <c r="C209" s="5"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="5"/>
+      <c r="B210" s="6"/>
+      <c r="C210" s="5"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="5"/>
+      <c r="B211" s="6"/>
+      <c r="C211" s="5"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="5"/>
+      <c r="B212" s="6"/>
+      <c r="C212" s="5"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="5"/>
+      <c r="B213" s="6"/>
+      <c r="C213" s="5"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="5"/>
+      <c r="B214" s="6"/>
+      <c r="C214" s="5"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="5"/>
+      <c r="B215" s="6"/>
+      <c r="C215" s="5"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="5"/>
+      <c r="B216" s="6"/>
+      <c r="C216" s="5"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="5"/>
+      <c r="B217" s="6"/>
+      <c r="C217" s="5"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="5"/>
+      <c r="B218" s="6"/>
+      <c r="C218" s="5"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="5"/>
+      <c r="B219" s="6"/>
+      <c r="C219" s="5"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="5"/>
+      <c r="B220" s="6"/>
+      <c r="C220" s="5"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="5"/>
+      <c r="B221" s="6"/>
+      <c r="C221" s="5"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="5"/>
+      <c r="B222" s="6"/>
+      <c r="C222" s="5"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="5"/>
+      <c r="B223" s="6"/>
+      <c r="C223" s="5"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="5"/>
+      <c r="B224" s="6"/>
+      <c r="C224" s="5"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="5"/>
+      <c r="B225" s="6"/>
+      <c r="C225" s="5"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="5"/>
+      <c r="B226" s="6"/>
+      <c r="C226" s="5"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="5"/>
+      <c r="B227" s="6"/>
+      <c r="C227" s="5"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="5"/>
+      <c r="B228" s="6"/>
+      <c r="C228" s="5"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="5"/>
+      <c r="B229" s="6"/>
+      <c r="C229" s="5"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="5"/>
+      <c r="B230" s="6"/>
+      <c r="C230" s="5"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="5"/>
+      <c r="B231" s="6"/>
+      <c r="C231" s="5"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="5"/>
+      <c r="B232" s="6"/>
+      <c r="C232" s="5"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="5"/>
+      <c r="B233" s="6"/>
+      <c r="C233" s="5"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="5"/>
+      <c r="B234" s="6"/>
+      <c r="C234" s="5"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="5"/>
+      <c r="B235" s="6"/>
+      <c r="C235" s="5"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="5"/>
+      <c r="B236" s="6"/>
+      <c r="C236" s="5"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="5"/>
+      <c r="B237" s="6"/>
+      <c r="C237" s="5"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="5"/>
+      <c r="B238" s="6"/>
+      <c r="C238" s="5"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="5"/>
+      <c r="B239" s="6"/>
+      <c r="C239" s="5"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="5"/>
+      <c r="B240" s="6"/>
+      <c r="C240" s="5"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="5"/>
+      <c r="B241" s="6"/>
+      <c r="C241" s="5"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="5"/>
+      <c r="B242" s="6"/>
+      <c r="C242" s="5"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="5"/>
+      <c r="B243" s="6"/>
+      <c r="C243" s="5"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="5"/>
+      <c r="B244" s="6"/>
+      <c r="C244" s="5"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="5"/>
+      <c r="B245" s="6"/>
+      <c r="C245" s="5"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="5"/>
+      <c r="B246" s="6"/>
+      <c r="C246" s="5"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="5"/>
+      <c r="B247" s="6"/>
+      <c r="C247" s="5"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="5"/>
+      <c r="B248" s="6"/>
+      <c r="C248" s="5"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="5"/>
+      <c r="B249" s="6"/>
+      <c r="C249" s="5"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="5"/>
+      <c r="B250" s="6"/>
+      <c r="C250" s="5"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="5"/>
+      <c r="B251" s="6"/>
+      <c r="C251" s="5"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="5"/>
+      <c r="B252" s="6"/>
+      <c r="C252" s="5"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="5"/>
+      <c r="B253" s="6"/>
+      <c r="C253" s="5"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="5"/>
+      <c r="B254" s="6"/>
+      <c r="C254" s="5"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="5"/>
+      <c r="B255" s="6"/>
+      <c r="C255" s="5"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="5"/>
+      <c r="B256" s="6"/>
+      <c r="C256" s="5"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="5"/>
+      <c r="B257" s="6"/>
+      <c r="C257" s="5"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="5"/>
+      <c r="B258" s="6"/>
+      <c r="C258" s="5"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="5"/>
+      <c r="B259" s="6"/>
+      <c r="C259" s="5"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="5"/>
+      <c r="B260" s="6"/>
+      <c r="C260" s="5"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="5"/>
+      <c r="B261" s="6"/>
+      <c r="C261" s="5"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="5"/>
+      <c r="B262" s="6"/>
+      <c r="C262" s="5"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="5"/>
+      <c r="B263" s="6"/>
+      <c r="C263" s="5"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="5"/>
+      <c r="B264" s="6"/>
+      <c r="C264" s="5"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="5"/>
+      <c r="B265" s="6"/>
+      <c r="C265" s="5"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="5"/>
+      <c r="B266" s="6"/>
+      <c r="C266" s="5"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="5"/>
+      <c r="B267" s="6"/>
+      <c r="C267" s="5"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="5"/>
+      <c r="B268" s="6"/>
+      <c r="C268" s="5"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="5"/>
+      <c r="B269" s="6"/>
+      <c r="C269" s="5"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="5"/>
+      <c r="B270" s="6"/>
+      <c r="C270" s="5"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="5"/>
+      <c r="B271" s="6"/>
+      <c r="C271" s="5"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="5"/>
+      <c r="B272" s="6"/>
+      <c r="C272" s="5"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="5"/>
+      <c r="B273" s="6"/>
+      <c r="C273" s="5"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="5"/>
+      <c r="B274" s="6"/>
+      <c r="C274" s="5"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="5"/>
+      <c r="B275" s="6"/>
+      <c r="C275" s="5"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="5"/>
+      <c r="B276" s="6"/>
+      <c r="C276" s="5"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="5"/>
+      <c r="B277" s="6"/>
+      <c r="C277" s="5"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="5"/>
+      <c r="B278" s="6"/>
+      <c r="C278" s="5"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="5"/>
+      <c r="B279" s="6"/>
+      <c r="C279" s="5"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="5"/>
+      <c r="B280" s="6"/>
+      <c r="C280" s="5"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="5"/>
+      <c r="B281" s="6"/>
+      <c r="C281" s="5"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="5"/>
+      <c r="B282" s="6"/>
+      <c r="C282" s="5"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="5"/>
+      <c r="B283" s="6"/>
+      <c r="C283" s="5"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="5"/>
+      <c r="B284" s="6"/>
+      <c r="C284" s="5"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="5"/>
+      <c r="B285" s="6"/>
+      <c r="C285" s="5"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="5"/>
+      <c r="B286" s="6"/>
+      <c r="C286" s="5"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="5"/>
+      <c r="B287" s="6"/>
+      <c r="C287" s="5"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="5"/>
+      <c r="B288" s="6"/>
+      <c r="C288" s="5"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="5"/>
+      <c r="B289" s="6"/>
+      <c r="C289" s="5"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="5"/>
+      <c r="B290" s="6"/>
+      <c r="C290" s="5"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="5"/>
+      <c r="B291" s="6"/>
+      <c r="C291" s="5"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="5"/>
+      <c r="B292" s="6"/>
+      <c r="C292" s="5"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="5"/>
+      <c r="B293" s="6"/>
+      <c r="C293" s="5"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="5"/>
+      <c r="B294" s="6"/>
+      <c r="C294" s="5"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="5"/>
+      <c r="B295" s="6"/>
+      <c r="C295" s="5"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="5"/>
+      <c r="B296" s="6"/>
+      <c r="C296" s="5"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="5"/>
+      <c r="B297" s="6"/>
+      <c r="C297" s="5"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="5"/>
+      <c r="B298" s="6"/>
+      <c r="C298" s="5"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="5"/>
+      <c r="B299" s="6"/>
+      <c r="C299" s="5"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="5"/>
+      <c r="B300" s="6"/>
+      <c r="C300" s="5"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="5"/>
+      <c r="B301" s="6"/>
+      <c r="C301" s="5"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E1"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" sqref="A2:A401">
+      <formula1>"2ЭС5К,3ЭС5К,4ЭС5К"</formula1>
+    </dataValidation>
+  </dataValidations>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E526"/>

--- a/zona_riska.xlsx
+++ b/zona_riska.xlsx
@@ -13682,7 +13682,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E102"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -13720,509 +13720,1721 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="5"/>
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 600</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="5"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="5"/>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 601</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="5"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="5"/>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 602</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="5"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="5"/>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 603</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="5"/>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 604</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="5"/>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 605</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="5"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="5"/>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 607</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="5"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="5"/>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 608</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="5"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="5"/>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 606</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="5"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="5"/>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 609</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="5"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="5"/>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 610</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="5"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="5"/>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 611</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="5"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="5"/>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 612</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="5"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="5"/>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 613</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="5"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="5"/>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 614</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="5"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="5"/>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 615</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="5"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="5"/>
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 616</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="5"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="5"/>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 617</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="5"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="5"/>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 618</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="5"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="5"/>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 619</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="5"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="5"/>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 620</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="5"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="5"/>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 621</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="5"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="5"/>
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 622</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="5"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="5"/>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 623</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="5"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="5"/>
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 624</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="5"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="5"/>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 625</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="5"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="5"/>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 626</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="5"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="5"/>
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 627</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="5"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="5"/>
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 628</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="5"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="5"/>
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 629</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="5"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="5"/>
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 630</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="5"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="5"/>
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 631</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="5"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="5"/>
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 632</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="5"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="5"/>
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 633</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="5"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="5"/>
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 634</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="5"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="5"/>
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 635</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="5"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="5"/>
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 636</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="5"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="5"/>
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 637</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="5"/>
-      <c r="B40" s="6"/>
-      <c r="C40" s="5"/>
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 638</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="5"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="5"/>
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 639</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="5"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="5"/>
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 640</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="5"/>
-      <c r="B43" s="6"/>
-      <c r="C43" s="5"/>
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 641</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="5"/>
-      <c r="B44" s="6"/>
-      <c r="C44" s="5"/>
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 642</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="5"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="5"/>
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 643</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="5"/>
-      <c r="B46" s="6"/>
-      <c r="C46" s="5"/>
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 644</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="5"/>
-      <c r="B47" s="6"/>
-      <c r="C47" s="5"/>
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 645</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="5"/>
-      <c r="B48" s="6"/>
-      <c r="C48" s="5"/>
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 646</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="5"/>
-      <c r="B49" s="6"/>
-      <c r="C49" s="5"/>
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 647</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="5"/>
-      <c r="B50" s="6"/>
-      <c r="C50" s="5"/>
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 648</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="5"/>
-      <c r="B51" s="6"/>
-      <c r="C51" s="5"/>
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 649</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="5"/>
-      <c r="B52" s="6"/>
-      <c r="C52" s="5"/>
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 650</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="5"/>
-      <c r="B53" s="6"/>
-      <c r="C53" s="5"/>
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 651</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-7 Абакан</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="5"/>
-      <c r="B54" s="6"/>
-      <c r="C54" s="5"/>
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 654</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="5"/>
-      <c r="B55" s="6"/>
-      <c r="C55" s="5"/>
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 652</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="5"/>
-      <c r="B56" s="6"/>
-      <c r="C56" s="5"/>
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 653</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="5"/>
-      <c r="B57" s="6"/>
-      <c r="C57" s="5"/>
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 655</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="5"/>
-      <c r="B58" s="6"/>
-      <c r="C58" s="5"/>
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 656</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="5"/>
-      <c r="B59" s="6"/>
-      <c r="C59" s="5"/>
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 657</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="5"/>
-      <c r="B60" s="6"/>
-      <c r="C60" s="5"/>
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 658</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="5"/>
-      <c r="B61" s="6"/>
-      <c r="C61" s="5"/>
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 659</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="5"/>
-      <c r="B62" s="6"/>
-      <c r="C62" s="5"/>
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 660</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="5"/>
-      <c r="B63" s="6"/>
-      <c r="C63" s="5"/>
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 661</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="5"/>
-      <c r="B64" s="6"/>
-      <c r="C64" s="5"/>
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 662</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="5"/>
-      <c r="B65" s="6"/>
-      <c r="C65" s="5"/>
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 663</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" s="5"/>
-      <c r="B66" s="6"/>
-      <c r="C66" s="5"/>
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 664</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" s="5"/>
-      <c r="B67" s="6"/>
-      <c r="C67" s="5"/>
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 665</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" s="5"/>
-      <c r="B68" s="6"/>
-      <c r="C68" s="5"/>
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 666</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" s="5"/>
-      <c r="B69" s="6"/>
-      <c r="C69" s="5"/>
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 667</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" s="5"/>
-      <c r="B70" s="6"/>
-      <c r="C70" s="5"/>
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 668</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" s="5"/>
-      <c r="B71" s="6"/>
-      <c r="C71" s="5"/>
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 669</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" s="5"/>
-      <c r="B72" s="6"/>
-      <c r="C72" s="5"/>
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 670</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" s="5"/>
-      <c r="B73" s="6"/>
-      <c r="C73" s="5"/>
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 671</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" s="5"/>
-      <c r="B74" s="6"/>
-      <c r="C74" s="5"/>
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 672</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" s="5"/>
-      <c r="B75" s="6"/>
-      <c r="C75" s="5"/>
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 673</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" s="5"/>
-      <c r="B76" s="6"/>
-      <c r="C76" s="5"/>
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 674</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" s="5"/>
-      <c r="B77" s="6"/>
-      <c r="C77" s="5"/>
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 675</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" s="5"/>
-      <c r="B78" s="6"/>
-      <c r="C78" s="5"/>
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 676</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" s="5"/>
-      <c r="B79" s="6"/>
-      <c r="C79" s="5"/>
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 677</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" s="5"/>
-      <c r="B80" s="6"/>
-      <c r="C80" s="5"/>
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 680</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="5"/>
-      <c r="B81" s="6"/>
-      <c r="C81" s="5"/>
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 679</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" s="5"/>
-      <c r="B82" s="6"/>
-      <c r="C82" s="5"/>
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 678</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" s="5"/>
-      <c r="B83" s="6"/>
-      <c r="C83" s="5"/>
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 681</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" s="5"/>
-      <c r="B84" s="6"/>
-      <c r="C84" s="5"/>
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 682</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" s="5"/>
-      <c r="B85" s="6"/>
-      <c r="C85" s="5"/>
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 683</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" s="5"/>
-      <c r="B86" s="6"/>
-      <c r="C86" s="5"/>
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 684</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" s="5"/>
-      <c r="B87" s="6"/>
-      <c r="C87" s="5"/>
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 685</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" s="5"/>
-      <c r="B88" s="6"/>
-      <c r="C88" s="5"/>
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 686</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" s="5"/>
-      <c r="B89" s="6"/>
-      <c r="C89" s="5"/>
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 687</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" s="5"/>
-      <c r="B90" s="6"/>
-      <c r="C90" s="5"/>
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 688</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" s="5"/>
-      <c r="B91" s="6"/>
-      <c r="C91" s="5"/>
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 689</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" s="5"/>
-      <c r="B92" s="6"/>
-      <c r="C92" s="5"/>
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 690</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" s="5"/>
-      <c r="B93" s="6"/>
-      <c r="C93" s="5"/>
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 691</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" s="5"/>
-      <c r="B94" s="6"/>
-      <c r="C94" s="5"/>
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 692</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" s="5"/>
-      <c r="B95" s="6"/>
-      <c r="C95" s="5"/>
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 693</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="96">
-      <c r="A96" s="5"/>
-      <c r="B96" s="6"/>
-      <c r="C96" s="5"/>
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 694</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" s="5"/>
-      <c r="B97" s="6"/>
-      <c r="C97" s="5"/>
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 695</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" s="5"/>
-      <c r="B98" s="6"/>
-      <c r="C98" s="5"/>
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 696</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" s="5"/>
-      <c r="B99" s="6"/>
-      <c r="C99" s="5"/>
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 697</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" s="5"/>
-      <c r="B100" s="6"/>
-      <c r="C100" s="5"/>
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 698</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" s="5"/>
-      <c r="B101" s="6"/>
-      <c r="C101" s="5"/>
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 699</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" s="5"/>
-      <c r="B102" s="6"/>
-      <c r="C102" s="5"/>
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ЭС5К</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 700</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ТЧЭ-1 Боготол</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="5"/>
@@ -15219,8 +16431,513 @@
       <c r="B301" s="6"/>
       <c r="C301" s="5"/>
     </row>
+    <row r="302">
+      <c r="A302" s="5"/>
+      <c r="B302" s="6"/>
+      <c r="C302" s="5"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="5"/>
+      <c r="B303" s="6"/>
+      <c r="C303" s="5"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="5"/>
+      <c r="B304" s="6"/>
+      <c r="C304" s="5"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="5"/>
+      <c r="B305" s="6"/>
+      <c r="C305" s="5"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="5"/>
+      <c r="B306" s="6"/>
+      <c r="C306" s="5"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="5"/>
+      <c r="B307" s="6"/>
+      <c r="C307" s="5"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="5"/>
+      <c r="B308" s="6"/>
+      <c r="C308" s="5"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="5"/>
+      <c r="B309" s="6"/>
+      <c r="C309" s="5"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="5"/>
+      <c r="B310" s="6"/>
+      <c r="C310" s="5"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="5"/>
+      <c r="B311" s="6"/>
+      <c r="C311" s="5"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="5"/>
+      <c r="B312" s="6"/>
+      <c r="C312" s="5"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="5"/>
+      <c r="B313" s="6"/>
+      <c r="C313" s="5"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="5"/>
+      <c r="B314" s="6"/>
+      <c r="C314" s="5"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="5"/>
+      <c r="B315" s="6"/>
+      <c r="C315" s="5"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="5"/>
+      <c r="B316" s="6"/>
+      <c r="C316" s="5"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="5"/>
+      <c r="B317" s="6"/>
+      <c r="C317" s="5"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="5"/>
+      <c r="B318" s="6"/>
+      <c r="C318" s="5"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="5"/>
+      <c r="B319" s="6"/>
+      <c r="C319" s="5"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="5"/>
+      <c r="B320" s="6"/>
+      <c r="C320" s="5"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="5"/>
+      <c r="B321" s="6"/>
+      <c r="C321" s="5"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="5"/>
+      <c r="B322" s="6"/>
+      <c r="C322" s="5"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="5"/>
+      <c r="B323" s="6"/>
+      <c r="C323" s="5"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="5"/>
+      <c r="B324" s="6"/>
+      <c r="C324" s="5"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="5"/>
+      <c r="B325" s="6"/>
+      <c r="C325" s="5"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="5"/>
+      <c r="B326" s="6"/>
+      <c r="C326" s="5"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="5"/>
+      <c r="B327" s="6"/>
+      <c r="C327" s="5"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="5"/>
+      <c r="B328" s="6"/>
+      <c r="C328" s="5"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="5"/>
+      <c r="B329" s="6"/>
+      <c r="C329" s="5"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="5"/>
+      <c r="B330" s="6"/>
+      <c r="C330" s="5"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="5"/>
+      <c r="B331" s="6"/>
+      <c r="C331" s="5"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="5"/>
+      <c r="B332" s="6"/>
+      <c r="C332" s="5"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="5"/>
+      <c r="B333" s="6"/>
+      <c r="C333" s="5"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="5"/>
+      <c r="B334" s="6"/>
+      <c r="C334" s="5"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="5"/>
+      <c r="B335" s="6"/>
+      <c r="C335" s="5"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="5"/>
+      <c r="B336" s="6"/>
+      <c r="C336" s="5"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="5"/>
+      <c r="B337" s="6"/>
+      <c r="C337" s="5"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="5"/>
+      <c r="B338" s="6"/>
+      <c r="C338" s="5"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="5"/>
+      <c r="B339" s="6"/>
+      <c r="C339" s="5"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="5"/>
+      <c r="B340" s="6"/>
+      <c r="C340" s="5"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="5"/>
+      <c r="B341" s="6"/>
+      <c r="C341" s="5"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="5"/>
+      <c r="B342" s="6"/>
+      <c r="C342" s="5"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="5"/>
+      <c r="B343" s="6"/>
+      <c r="C343" s="5"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="5"/>
+      <c r="B344" s="6"/>
+      <c r="C344" s="5"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="5"/>
+      <c r="B345" s="6"/>
+      <c r="C345" s="5"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="5"/>
+      <c r="B346" s="6"/>
+      <c r="C346" s="5"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="5"/>
+      <c r="B347" s="6"/>
+      <c r="C347" s="5"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="5"/>
+      <c r="B348" s="6"/>
+      <c r="C348" s="5"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="5"/>
+      <c r="B349" s="6"/>
+      <c r="C349" s="5"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="5"/>
+      <c r="B350" s="6"/>
+      <c r="C350" s="5"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="5"/>
+      <c r="B351" s="6"/>
+      <c r="C351" s="5"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="5"/>
+      <c r="B352" s="6"/>
+      <c r="C352" s="5"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="5"/>
+      <c r="B353" s="6"/>
+      <c r="C353" s="5"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="5"/>
+      <c r="B354" s="6"/>
+      <c r="C354" s="5"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="5"/>
+      <c r="B355" s="6"/>
+      <c r="C355" s="5"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="5"/>
+      <c r="B356" s="6"/>
+      <c r="C356" s="5"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="5"/>
+      <c r="B357" s="6"/>
+      <c r="C357" s="5"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="5"/>
+      <c r="B358" s="6"/>
+      <c r="C358" s="5"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="5"/>
+      <c r="B359" s="6"/>
+      <c r="C359" s="5"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="5"/>
+      <c r="B360" s="6"/>
+      <c r="C360" s="5"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="5"/>
+      <c r="B361" s="6"/>
+      <c r="C361" s="5"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="5"/>
+      <c r="B362" s="6"/>
+      <c r="C362" s="5"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="5"/>
+      <c r="B363" s="6"/>
+      <c r="C363" s="5"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="5"/>
+      <c r="B364" s="6"/>
+      <c r="C364" s="5"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="5"/>
+      <c r="B365" s="6"/>
+      <c r="C365" s="5"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="5"/>
+      <c r="B366" s="6"/>
+      <c r="C366" s="5"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="5"/>
+      <c r="B367" s="6"/>
+      <c r="C367" s="5"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="5"/>
+      <c r="B368" s="6"/>
+      <c r="C368" s="5"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="5"/>
+      <c r="B369" s="6"/>
+      <c r="C369" s="5"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="5"/>
+      <c r="B370" s="6"/>
+      <c r="C370" s="5"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="5"/>
+      <c r="B371" s="6"/>
+      <c r="C371" s="5"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="5"/>
+      <c r="B372" s="6"/>
+      <c r="C372" s="5"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="5"/>
+      <c r="B373" s="6"/>
+      <c r="C373" s="5"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="5"/>
+      <c r="B374" s="6"/>
+      <c r="C374" s="5"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="5"/>
+      <c r="B375" s="6"/>
+      <c r="C375" s="5"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="5"/>
+      <c r="B376" s="6"/>
+      <c r="C376" s="5"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="5"/>
+      <c r="B377" s="6"/>
+      <c r="C377" s="5"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="5"/>
+      <c r="B378" s="6"/>
+      <c r="C378" s="5"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="5"/>
+      <c r="B379" s="6"/>
+      <c r="C379" s="5"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="5"/>
+      <c r="B380" s="6"/>
+      <c r="C380" s="5"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="5"/>
+      <c r="B381" s="6"/>
+      <c r="C381" s="5"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="5"/>
+      <c r="B382" s="6"/>
+      <c r="C382" s="5"/>
+    </row>
+    <row r="383">
+      <c r="A383" s="5"/>
+      <c r="B383" s="6"/>
+      <c r="C383" s="5"/>
+    </row>
+    <row r="384">
+      <c r="A384" s="5"/>
+      <c r="B384" s="6"/>
+      <c r="C384" s="5"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="5"/>
+      <c r="B385" s="6"/>
+      <c r="C385" s="5"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="5"/>
+      <c r="B386" s="6"/>
+      <c r="C386" s="5"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="5"/>
+      <c r="B387" s="6"/>
+      <c r="C387" s="5"/>
+    </row>
+    <row r="388">
+      <c r="A388" s="5"/>
+      <c r="B388" s="6"/>
+      <c r="C388" s="5"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="5"/>
+      <c r="B389" s="6"/>
+      <c r="C389" s="5"/>
+    </row>
+    <row r="390">
+      <c r="A390" s="5"/>
+      <c r="B390" s="6"/>
+      <c r="C390" s="5"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="5"/>
+      <c r="B391" s="6"/>
+      <c r="C391" s="5"/>
+    </row>
+    <row r="392">
+      <c r="A392" s="5"/>
+      <c r="B392" s="6"/>
+      <c r="C392" s="5"/>
+    </row>
+    <row r="393">
+      <c r="A393" s="5"/>
+      <c r="B393" s="6"/>
+      <c r="C393" s="5"/>
+    </row>
+    <row r="394">
+      <c r="A394" s="5"/>
+      <c r="B394" s="6"/>
+      <c r="C394" s="5"/>
+    </row>
+    <row r="395">
+      <c r="A395" s="5"/>
+      <c r="B395" s="6"/>
+      <c r="C395" s="5"/>
+    </row>
+    <row r="396">
+      <c r="A396" s="5"/>
+      <c r="B396" s="6"/>
+      <c r="C396" s="5"/>
+    </row>
+    <row r="397">
+      <c r="A397" s="5"/>
+      <c r="B397" s="6"/>
+      <c r="C397" s="5"/>
+    </row>
+    <row r="398">
+      <c r="A398" s="5"/>
+      <c r="B398" s="6"/>
+      <c r="C398" s="5"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="5"/>
+      <c r="B399" s="6"/>
+      <c r="C399" s="5"/>
+    </row>
+    <row r="400">
+      <c r="A400" s="5"/>
+      <c r="B400" s="6"/>
+      <c r="C400" s="5"/>
+    </row>
+    <row r="401">
+      <c r="A401" s="5"/>
+      <c r="B401" s="6"/>
+      <c r="C401" s="5"/>
+    </row>
+    <row r="402">
+      <c r="A402" s="5"/>
+      <c r="B402" s="6"/>
+      <c r="C402" s="5"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1"/>
+  <autoFilter ref="A1:E102"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="A2:A401">
       <formula1>"2ЭС5К,3ЭС5К,4ЭС5К"</formula1>
